--- a/smi/catalogo_SMI.xlsx
+++ b/smi/catalogo_SMI.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_01.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_01.html</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_02.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_02.html</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_03.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_03.html</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_04.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_04.html</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_05.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_05.html</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_06.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_06.html</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_07.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_07.html</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_08.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_08.html</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_09.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_09.html</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_10.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_10.html</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_11.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_11.html</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_12.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_12.html</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_13.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_13.html</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_14.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_14.html</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_15.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_15.html</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_16.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_16.html</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_17.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_17.html</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_18.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_18.html</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_19.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_19.html</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_20.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_20.html</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_21.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_21.html</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_22.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_22.html</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_23.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_23.html</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_24.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_24.html</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_25.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_25.html</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_26.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_26.html</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_27.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_27.html</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_28.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_28.html</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_29.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_29.html</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_30.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_30.html</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_31.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_31.html</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_32.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_32.html</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_33.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_33.html</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_34.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_34.html</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_35.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_35.html</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_36.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_36.html</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_37.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_37.html</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_38.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_38.html</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_39.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_39.html</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_40.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_40.html</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_41.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_41.html</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_42.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_42.html</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_43.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_43.html</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_44.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_44.html</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_45.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_45.html</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       <c r="O47" s="3" t="inlineStr"/>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_46.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_46.html</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_47.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_47.html</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_48.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_48.html</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_49.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_49.html</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       <c r="O51" s="3" t="inlineStr"/>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_50.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_50.html</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_51.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_51.html</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_52.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_52.html</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_53.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_53.html</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_54.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_54.html</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_55.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_55.html</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_56.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_56.html</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_57.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_57.html</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_58.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_58.html</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_59.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_59.html</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_60.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_60.html</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_61.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_61.html</t>
         </is>
       </c>
     </row>
@@ -4741,11 +4741,7 @@
           <t>Primario</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Prevenir a desnutrição  aguda, reduzir mortalidade infantil</t>
@@ -4784,7 +4780,7 @@
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_62.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_62.html</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4862,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_63.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_63.html</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4940,7 @@
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_64.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_64.html</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5018,7 @@
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_65.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_65.html</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5096,7 @@
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_66.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_66.html</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5178,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_67.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_67.html</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5256,7 @@
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_68.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_68.html</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5318,7 @@
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_69.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_69.html</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5388,7 @@
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_70.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_70.html</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5442,7 @@
       <c r="O72" s="2" t="inlineStr"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_71.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_71.html</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5516,7 @@
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_72.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_72.html</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5590,7 @@
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_73.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_73.html</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5652,7 @@
       <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_74.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_74.html</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5726,7 @@
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_75.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_75.html</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5800,7 @@
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_76.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_76.html</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5858,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_77.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_77.html</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5916,7 @@
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_78.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_78.html</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5974,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_79.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_79.html</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6032,7 @@
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_80.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_80.html</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6091,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_81.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_81.html</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6153,7 @@
       <c r="O83" s="3" t="inlineStr"/>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_82.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_82.html</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6215,7 @@
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_83.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_83.html</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6273,7 @@
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_84.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_84.html</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6331,7 @@
       <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_85.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_85.html</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6393,7 @@
       <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_86.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_86.html</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6451,7 @@
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_87.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_87.html</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6509,7 @@
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>https://kaiserso.github.io/INS_delphi/malaria/smi_88.html</t>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_88.html</t>
         </is>
       </c>
     </row>

--- a/smi/catalogo_SMI.xlsx
+++ b/smi/catalogo_SMI.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -578,12 +578,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Especuloscopia (Espéculos)</t>
+          <t>Anamnese, Exame físico e  Especuloscopia (Espéculos)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -591,15 +591,19 @@
           <t>1976</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2.111.754</t>
+          <t>1.700.000</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>16.054.555</t>
+          <t>1.292.000</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -607,10 +611,14 @@
           <t>76.0%</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Tem havido falta de AAS de 100 mg, pelo que orientamos que seja utilizado o comprimido de 500 mg, partido em 4 partes e toma de 1 parte diária, que não é aconselhável por causa da concentracao do produto em cada parte e desatencao da mulher. Faltam esfigmomanómetros, balanças</t>
+          <t>Faltam calendário obstétrico, ecógrafo e ESMI capacitadas no cálculo do tempo de gestacao</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -647,17 +655,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Pimário</t>
+          <t>Primário</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Esfigmomanómetro,  fita métrica, dopller, Pinard, ecógrafo, medicamentos: antibióticos, tocolíticos e anti-hipertensivos</t>
+          <t>Anamnese, cálculo da Idade gestacional, teste de gravidez, teste de urina, balanca com altímetro, esfigmomanómetro,  fita métrica, Pinard, ecógrafo, medicamentos: antibióticos, tocolíticos e anti-hipertensivos, Dexametasona e AAS 100 mg</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -672,21 +680,29 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>1.605.455</t>
+          <t>122.400</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>80.273</t>
+          <t>24.480</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Relutância das ESMI em não encaminhar grávidas ARO para o clinico dentro da mesma US.</t>
+        </is>
+      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_02.html</t>
@@ -726,33 +742,45 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Fita de perímetro braquial, Balança de adulto, Altímetro</t>
+          <t>Fita de perímetro braquial, Balança de adulto com Altímetro</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>S/I</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>S/I</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Area coberta pelo Departamento de Nutricao</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_03.html</t>
@@ -793,12 +821,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Sulfadoxina e Pirimetamina</t>
+          <t>Comprimidos de Sulfadoxina e Pirimetamina, copos e água para  (DOT - directa observacao pelo trabalhador de saúde)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -806,15 +834,19 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2.111.754</t>
+          <t>1.700.000</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>1.898.500</t>
+          <t>1.530.000</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -822,7 +854,11 @@
           <t>90.0%</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -869,7 +905,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -877,15 +913,19 @@
           <t>1976</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>UNICEF</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2.111.754</t>
+          <t>595.000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1.640.413</t>
+          <t>162.435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -893,7 +933,11 @@
           <t>78.0%</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -934,12 +978,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AAS 100 mg</t>
+          <t xml:space="preserve"> AAS 100 mg de aacordo com o protocolo</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -947,23 +991,31 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>85.000</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2.550</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1004,12 +1056,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dexametasona</t>
+          <t>Diagnóstico de Ameaca de parto Pretermo e Administracao de Dexametasona</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1017,23 +1069,31 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>68.000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2.040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1074,12 +1134,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>ARVs</t>
+          <t>Testagem e aconselhamento. ARVs</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1087,7 +1147,11 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>2.156.280</t>
@@ -1134,7 +1198,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ttratamento do HIV </t>
+          <t xml:space="preserve">Tratamento do HIV </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1144,12 +1208,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ARVs</t>
+          <t>ARVs. Medicamentos para doencas oportunistas.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduzir a morbidade, mortalidade e reduzir sequelas maternas </t>
+          <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1157,23 +1221,31 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>109.687</t>
+          <t>391.000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109.662</t>
+          <t>387.000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1214,12 +1286,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Infraestruturas adequadas  com corredor e equipada. Camas articuladas suficientes, Ecógrafo, Dopller,  fita métrica, fita de nastro, pera de aspiracao nasal de RN , candeeiro ginecológico,  aparelho de CTG,  Pinard, lencois, arrastadeiras, resguardos, biombo,  ventosas, kits de parto, Kits de cesariana, kits de laparotomia, medicamentos: antibióticos injectáveis, , anti-convulsivantes, anestésicos, Dexametasona,  equipamento de reanimação materna e neonatal, carro de anestesia, instrumentos de registo, RH qualificados e habilitados,  insumos, clorexidina gel 7.1%, ARV, aparelho de   Hemocue</t>
+          <t>Infraestruturas adequadas  com corredor amplo para passar maca e para a mulher caminhar, equipada. Camas articuladas suficientes, colchões, lencois e mantas. Ecógrafo, Dopller,  fita métrica, fita de nastro, clamps para cordão umbilical,pera de aspiracao nasal de RN , candeeiro ginecológico,  aparelho de CTG,  Pinard,  arrastadeiras, resguardos,  kits de parto suficientes, Kits de episiorrafia, Kits de cesariana se com Bloco Operatório, kits de laparotomia, medicamentos: antibióticos injectáveis, anti-convulsivantes, anestésicos, Dexametasona,  equipamento de reanimação materna e neonatal, carro de anestesia, instrumentos de registo, RH qualificados e habilitados,  insumos, clorexidina gel 7.1%, ARV, aparelho de   Hemocue,cacifos e armários, mesa e cadeiras.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao parto seguro, monitorar as complicações intra e pós parto imediato e reduzir a incidencia da mortalidade materna e perinatal</t>
+          <t>Garantir a saúde da mulher e seu futuro reprodutivo</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1227,15 +1299,19 @@
           <t>1975</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>MISAU e parceiros</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>1.495.999</t>
+          <t>1.530.000</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>1.404.050</t>
+          <t>1.438.200</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1243,10 +1319,14 @@
           <t>93,9%</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Ha falta de Kits de parto e outro material medico coirurgico, marquezas, roupa de cama em maior numero das  Unidades sanitarias, ventosas, partogramas e outros instrumentos de registo</t>
+          <t>Ha falta de Kits de parto e outro material medico coirurgico, marquezas, roupa de cama na quase totalidade das  Unidades Sanitarias, ventosas, partogramas, diário clinico e de enfermagen, requisicao de análises, bloco de receitas, instrumentos de registo.</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1278,7 +1358,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Monitoria da saúde da mãe e do recém-nascido nas 1as 2 horas até 24 horas pós nascimento</t>
+          <t>Monitoria da saúde da mãe e do recém-nascido na 1a e pós-parto mediato. Controle até a alta, 24 horas pós nascimento.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1288,12 +1368,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Kits de episiorrafia, medicamentos, sangue sos (reagentes), soros, antibióticos, anti-hipertensivos, anti-convulsivantes, esfigmomanómetros, arrastadeira, consumíveis, biombos</t>
+          <t>ESMI suficientese capacitadas na US, camas, lencois, medicamentos, sangue sos (reagentes), soros, antibióticos, anti-hipertensivos, anti-convulsivantes, gabinete para a 1a consulta pós-parto e pós-natal que deve ser feita na maternidade, esfigmomanómetros, arrastadeira, consumíveis, biombos</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao parto seguro, monitorar as complicações intra e pós parto imediato e reduzir a incidencia da mortalidade materna e perinatal</t>
+          <t>Garantir a saúde da mulher e seu futuro reprodutivo</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1301,26 +1381,34 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1.404.050</t>
+          <t>1.615.000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1.331.333</t>
+          <t>1.324.300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94.8%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>82.0%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tem havido falta da Dexametasona nas unmidades saanitárias </t>
+          <t>Há escassez severa de tudo nas US</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1368,7 +1456,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao parto seguro, monitorar as complicações intra e pós parto imediato e reduzir a incidencia da mortalidade materna e perinatal</t>
+          <t>Garantir a saúde da mulher e seu futuro reprodutivo</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1383,18 +1471,24 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
+          <t>1.700.000</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>1.402.500</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>82.5%</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>1.403.304</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tem défice de espéculos em algumas unidades Sanitárias e algumas sem autoclave para a esterilização do material. Dependendo de uma outra unidade sanitária mais proxima para esterilizar.  Por falta do material as ESMI optam por usar condutas proibidas que é o toque vaginal. </t>
@@ -1429,22 +1523,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Reduzir o abortos inseguros e a morbi mortalidade materna por abortos</t>
+          <t>Reduzir os abortos inseguros e a morbi mortalidade materna por aborto</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Todos os níveis de atencao em saúde</t>
+          <t>todos os níveis de atencao em saúde</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Miso-Mife, Especulos, seringas de aspiracao , lampadas ginecologicas e outro material do kit de ginecologia</t>
+          <t>Comprimido abortivo Miso-Mife, Especulos, seringas de aspiracao , lampadas ginecologicas e outro material do kit de ginecologia</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao parto seguro, monitorar as complicações intra e pós parto imediato e reduzir a incidencia da mortalidade materna e perinatal</t>
+          <t>Garantir a saúde da mulher e seu futuro reprodutivo</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1452,19 +1546,32 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parceiros
+</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1.360.000</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>170.000</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>20.400</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Tem havido falta do Miso-Mife, dificultando a provisao dos servicos</t>
@@ -1509,12 +1616,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Espéculos, valvula de Sims, pinça de Pozzi, pinça de Foerster (restos), antibióticos, analgésicos, kit de AMIU</t>
+          <t>ESMI suficientes e capacitadas. Espéculos, valvula de Sims, pinça de Pozzi, pinça de Foerster (restos), antibióticos, analgésicos, kit de AMIU</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>reduzir incidencia de mortalidade materna, reduzir gravidez nao desejado</t>
+          <t>reduzir incidencia de morte materna, reduzir gravidez nao desejado</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1522,23 +1629,32 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parceiros
+</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>8.311.105</t>
+          <t>170.000</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>63.660</t>
+          <t>62.900</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -1592,7 +1708,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>MISAU E Parceiros</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
           <t>8.159.149</t>
@@ -1600,15 +1720,19 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251.977</t>
+          <t>244.775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -1634,12 +1758,13 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Prevenção da infecção do coto umbilical</t>
+          <t xml:space="preserve">Prevenção da infecção do coto umbilical
+</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1652,12 +1777,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Aplicação de Clorexidina Gel 7.1% no coto umbilical,  após ao nascimento, 1 vez ao dia, até completar 7 dias.</t>
+          <t>Inclui: prevenção da infecção do coto umbilical; Aplicação de Clorexidina Gel 7.1% no coto umbilical,  após ao nascimento, 1 vez ao dia, até completar 7 dias.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a mortalidade neonatal</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1721,7 +1846,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1739,15 +1864,19 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Aplicação ocular da pomada de tetraciclina (1%) dentro da 1ª hora logo após o nascimento</t>
+          <t>Aplicação ocular da pomada de tetraciclina (1%)  logo após o nascimento</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>MISAU</t>
@@ -1760,16 +1889,20 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1.333.729</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>O número de crianças que recebeu Tetraciclina Pomada Oftálmica não vêm refletido no SIS-MA</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_17.html</t>
@@ -1794,7 +1927,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1819,10 +1952,14 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>MISAU</t>
@@ -1833,10 +1970,22 @@
           <t>1.401.849</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>O número de crianças que recebeu Vitamina K não vêm refletido no SIS-MA</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_18.html</t>
@@ -1861,7 +2010,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1879,15 +2028,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Unidade de calor radiante (aquecedor eléctrico)</t>
+          <t>Contacto imediato pele-a-pele</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2009 (contacto pele-a-pele)</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
@@ -1895,11 +2048,19 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1.401.849</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>1342273 (Partos eutócicos)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1.333.729</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
@@ -1926,17 +2087,20 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Manejo da exposição ao HIV</t>
+          <t>Manejo da exposição ao HIV (Prevenção da Transmissão Vertical do HIV)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primário
+Secundário
+Terciário
+Quartenário</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1947,7 +2111,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a mortalidade neonatal</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1962,7 +2126,7 @@
       <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Quantificação dos Arvs  feitos ao nível do Programa Nacional de Controle de ITS/HIV-SIDA</t>
+          <t>Quantificação dos Arvs feitos ao nível do Programa Nacional de Controle de ITS/HIV-SIDA</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
@@ -1989,7 +2153,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1999,23 +2163,26 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primário
+Secundário
+Terciário
+Quartenário</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Melhoria da assistência ao Recém-nascido com asfixia neonatal assegurando a formação contínua dos profissionais de saúde e compra de material (cantinho de reanimação).
-Cantinho de reanimação nas maternidades, composto por: ambu e máscara tamanho 0 e 1; seringa de 5 ml, dextrose a 5%, a 30% e a 50%; ampicilina e gentamicina; concentrador de oxigénio; campus estéreis; sonda para oxigénio e sonda para alimentação</t>
+Cantinho de reanimação nas maternidades, composto por: ambu e máscara tamanho 0 e 1; seringa de 5 ml, dextrose a 5%, a 30% e a 50%; ampicilina e gentamicina; concentrador de oxigénio; campus estéreis; sonda para oxigénio; sonda para alimentação e fonte de calor radiante</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a mortalidade neonatal</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2010 (normas de Reanimação Neonatal)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2039,11 +2206,7 @@
           <t>98.0%</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>144.28 USD</t>
-        </is>
-      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
@@ -2069,46 +2232,54 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Reforço da atenção e os cuidados para Recém-nascidos prematuros (˂ 37 semanas de gestação) e de Baixo Peso à nascença (˂ 2500 gramas)</t>
+          <t xml:space="preserve">Reforço da atenção e os cuidados para Recém-nascidos prematuros (˂ 37 semanas de gestação) </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primário
+Secundário
+Terciário
+Quartenário</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expansão e revitalização de unidades Canguru nas maternidades: </t>
+          <t>Inclui prestar cuidados de MMC (métodos mãe canguru) por forma a garantir a sobrevivência e redução da morbilidade e mortalidade neonatal)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>1984 (MMC)</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>UNICEF
+OMS</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>1.401.849</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.330.158</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>94.9%</t>
-        </is>
-      </c>
+          <t>17.014</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr">
@@ -2135,42 +2306,54 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Assistência ao Recém-Nascido na Sala de Parto</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Exame físico geral do Recém-Nascido</t>
+          <t>Reforço da atenção e os cuidados para Recém-nascidos de Baixo Peso à nascença (˂ 2500 gramas)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primário
+Secundário
+Terciário
+Quartenário</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Termómetro, Cronómetros, balanças pediátricas, fita de perímetro craniano</t>
+          <t>Inclui prestar cuidados de MMC (métodos mãe canguru) por forma a garantir a sobrevivência e redução da morbilidade e mortalidade neonatal)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1984 (MMC)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>UNICEF
+OMS</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1.401.849</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>98.0%</t>
-        </is>
-      </c>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>33.775</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
@@ -2197,37 +2380,54 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Atenção Integrada as Doenças Neonatais (AIDI NN)  até aos 7 dias de vida</t>
+          <t>Assistência ao Recém-Nascido na Sala de Parto/AIDI NN (Atenção Integrada às doenças da infância dos 0 aos 7 dias de vida)</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Avaliar, classificar e tratar as doenças neonatais</t>
+          <t>Exame físico geral do Recém-Nascido</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primário
+Secundário
+Terciário
+Quartenário</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Administração de Ampicilina, gentamicina e oxigénio</t>
+          <t xml:space="preserve">
+O exame físico geral do recém-nascido é uma avaliação clínica completa, com o objetivo de identificar sinais de normalidade e detectar precocemente qualquer problema de saúde.
+Aparência geral: cor da pele, presença de cianose ou icterícia, hidratação.
+Sinais vitais: frequência respiratória, frequência cardíaca, temperatura.
+Tônus e postura: atividade motora, reflexos primitivos (como reflexo de sucção e reflexo de Moro).
+Cabeça e face: fontanelas, suturas, formato da cabeça, olhos, ouvidos, nariz e boca.
+Tórax e abdómen: inspeção e palpação de coração, pulmões, fígado e baço.
+Genitália e períneo: presença de anomalias genitais ou sinais de infecção.
+Extremidades e coluna: simetria, mobilidade, malformações.
+Coto umbilical: aspecto, sinais de sangramento ou infeção.
+</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
+          <t>Reduzir a mortalidade neonatal</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>1.401.849</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr"/>
@@ -2255,34 +2455,34 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atenção Integrada as Doenças Neonatais (AIDI NN)  até aos 7 dias de vida </t>
+          <t xml:space="preserve">Atenção Integrada às Doenças da Infânica, dos 0 aos 7 dias de vida (AIDI NN) </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Revitalizar os berçarios à nível rural e distrital</t>
+          <t>Manejo correcto das patologias neonatais</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primário
-Secundário
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Avaliar, classificar e tratar as doenças neonatais
 </t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Construção e ou apetrechamento incluindo alocação de material e equipamento, assim como formação contínua dos profissionais de saúde</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a mortalidade neonatal</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2295,27 +2495,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>128 berçários</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32 berçarios</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>12023USD</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não temos metas para neonatais doentes e não existiam até 2024 os livros de registo de internamento de neonatologia </t>
-        </is>
-      </c>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_25.html</t>
@@ -2345,7 +2535,8 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Avaliação do crescimento (Peso, altura/estatura, perímetro braquial e tabelas de avaliação)</t>
+          <t>Verificação do estado de 
+saúde, crescimento e desenvolvimento da criança</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -2356,7 +2547,7 @@
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">
-Inclui o uso de: balanço de prato; balança pêndulo; altímetro; fitas para avaliação do perímetro braquial
+Inclui a: Avaliação do crescimento; Avaliação do desenvolvimento psicomotor; Realização de exame físico completo; Promoção do cumprimento do calendário vacinal; Orientação sobre a alimentação adequada da criança; Prevenção das deficiências em micronutrientes; Suplementação com Vitamina A e desparasitação; Educação sanitária individual;Rastreio de factores de risco para a CCR; Recomendações sobre o planeamento familiar.
 </t>
         </is>
       </c>
@@ -2365,11 +2556,34 @@
           <t>Reduzir a mortalidade infantil</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>PATH
+ OMS
+ UNICEF
+ Alcançar/FHI 360</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>5262815 (INE: 0-59 meses)</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>1739751 (0-59 MESES)</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>33.0%</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr">
@@ -2396,12 +2610,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normas de atenção a criança sadia </t>
+          <t>Normas de atenção a criança em risco</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avaliação do desenvolvimento psicomotor </t>
+          <t>Atendimento personalizado e adequado as crianças  mais vulneráveis: Crianças expostas ao HIV; Crianças expostas a Sífilis; Crianças com contacto de tuberculose pulmonar; Crianças com crescimento insuficiente ou desnutrição; Crianças com peso inferior a 2500 gramas à nascença, gémeos, crianças com desmame antes dos 12 meses de idade e/ou em aleitamento artificial; Criança com atraso de desenvolvimento psicomotor; Crianças órfãs e vulneráveis.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2411,7 +2625,10 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Utilização das ferramentas de avaliação do crescimento e desenvolvimento: formação dos profissionais de saúde para o uso da Ferramenta MDAT-IDEC</t>
+          <t xml:space="preserve">A conduta a ter nas crianças em risco depende do motivo, entretanto existem actividades que devem ser desempenhadas de um modo geral em todas as crianças independentemente do tipo de problema que se apresenta, 
+nomeadamente: 
+Controle do peso, medições antropométricas e avaliação do desenvolvimento psicomotor;  Garantir o cumprimento do calendário de vacinação; Atribuição do NID e introdução dos dados da criança no livro de CCR; Abertura e actualização da ficha individual da criança em risco; Preenchimento detalhado das guias em caso de referência/transferência da criança para outro lugar/sector;  anotação das informações relevantes (Prevenção de Transmissão Vertical do HIV e Sífilis da mãe e criança, Testagem da criança, Profilaxias do recém-nascido com ARVs e Cotrimoxazol, PTV da mãe, Parâmetros de Desenvolvimento Psicomotor, Parâmetros Antropométricos) no cartão de saúde da criança e na ficha individual ou processo clínico da criança; aconselhamento e testagem de HIV (a tidas as crianças e seus cuidadores); aconselhamento em alimentação infantil, boas prácticas de higiene, actividades estimulantes, etc.
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2419,33 +2636,28 @@
           <t>Reduzir a mortalidade infantil</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATH
+          <t>PATH
  OMS
  UNICEF
- Alcançar/FHI 360
-</t>
+ Alcançar/FHI 360</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1.739.751</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>16.060.835</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sem registo nos nossos instrumentos, das crianças que tenham sido submetidas ao uso destas ferramentas de avaliação </t>
-        </is>
-      </c>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_27.html</t>
@@ -2470,12 +2682,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Normas de atenção a criança sadia </t>
+          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Monitoria e Avaliação</t>
+          <t>Manejo correcto das doenças da Infância</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2485,7 +2697,9 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Reprodução dos livros de registo da consulta da criança sadia; livros de resumo diário e mensal da unidade sanitária e cartões de saúde</t>
+          <t xml:space="preserve">
+Avaliar, classificar e tratar as doenças da infância
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2493,611 +2707,12 @@
           <t>Reduzir a mortalidade infantil</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_28.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>smi_29</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Chamadas telefónicas e visitas domiciliares das crianças em risco</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Créditos para comunicação</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_29.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>smi_30</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Normas de atenção a criança em risco </t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Avaliação do crescimento: (Peso, altura/estatura, perímetro braquial e tabelas de avaliação)</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inclui: balanço de prato; balança pêndulo; altímetro; fitas para avaliação do perímetro braquial
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_30.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>smi_31</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Avaliação do desenvolvimento psicomotor: Utilização das ferramentas de avaliação do crescimento e desenvolvimento:</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Utilização das ferramentas de avaliação do crescimento e desenvolvimento: formação dos profissionais de saúde para o uso da Ferramenta MDAT-IDEC</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-PATH
- OMS
- UNICEF
- Alcançar/FHI 360
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1.739.751</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sem registo nos nossos instrumentos, das crianças que tenham sido submetidas ao uso destas ferramentas de avaliação </t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_31.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>smi_32</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Avaliação do desenvolvimento psicomotor: utilização de materiais necessários para monitoria de desenvolvimento na CCS</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Impressão e distribuição de: Cartaz de ‘’Marcos de desenvolvimento’’; Cartaz ‘’Recomendações de cuidados para o desenvolvimento’’</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_32.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>smi_33</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Manejo da criança exposta ao HIV</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Administração de ARVs para profilaxia para o HIV
-Testes de HIV
-Testes de PCR</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>101.379</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Quantificação dos Arvs e outros insumos feitos ao nível do Programa Nacional de Controle de ITS/HIV-SIDA</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_33.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>smi_34</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Manejo da criança em contacto com  Tuberculose</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Adminstração de TPT</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>96.748</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>76.964</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>79.5%</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>Quantificação do medicamento usado para TPT ao nível do programa da Tuberculose</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_34.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>smi_35</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Manejo da criança com desnutrição aguda moderada</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>71.584</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Gestão ao nível do Departamento de nutrição</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_35.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>smi_36</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Manejo da criança com desnutrição aguda grave</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>42.516</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>Gestão ao nível do Departamento de nutrição</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_36.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>smi_37</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Normas de atenção a criança em risco</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Monitoria e Avaliação</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução dos livros de registo da consulta da criança em risco; ficha individual da criança na CCR e resumo mensal da CCR</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_37.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>smi_38</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Infantil</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Manejo da criança dos 0-59meses com diarreia</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primário
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Administratação de SRO+Zinco (kit) em crianças dos 0-59 meses
- </t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">UNICEF
  CHAI
@@ -3106,26 +2721,656 @@
 </t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>260.077</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>155.141</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>59.7%</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>0.4 (USD)</t>
-        </is>
-      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Atendidos na CCD</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_28.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>smi_29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oferta de Contraceptivos orais combinados -  Microgynon (Etinilestradiol 0.03mg+0.15mg),comprimidos </t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consiste na aquisição/compra e oferta  de Microgynon (Etinilestradiol 0.03mg+0.15mg), ciclos  </t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>MIF's= 8159149</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido= 361599</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_29.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>smi_30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oferta de Contraceptivos orais só com progesterona -  Microgynon (Etinilestradiol 0.03mg+0.15mg),comprimidos </t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Microlut( Levonorgestrel 30mcg), ciclos</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_30.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>smi_31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Sayana Press 104mg/0.65mg, injectável</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Consite na aquisição/compra e oferta de Sayana Press 104mg/0.65mg, injectável</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido = 1234207</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_31.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>smi_32</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Depo-Provera(Medroxiprogesterona 150mg/ml), injectavel</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Depo-Provera (Medroxiprogesterona 150mg/ml), injectável</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_32.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>smi_33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Levoplant 75mg, implante</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Levoplant 75mg, implante</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_33.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>smi_34</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Jadelle (Levonorgestrel 2*75mg), implante</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Jadelle (Levonorgestrel 2*75mg), implante</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>8.159.149</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido= 2650599</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_34.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>smi_35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Implanon (Etonogestrel 68mg),implante</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Implanon (Etonogestrel 68mg), Implante</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido= 335980</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_35.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>smi_36</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Copper T380 0.2%, DIU</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de Copper T380 0.2%, DIU</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido= 974344</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_36.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>smi_37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Preservativos masculinos, para dupla proteção</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de preservativos masculinos para a dupla protecção</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/smi/smi_37.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>smi_38</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Planeamento Familiar</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de Preservativos femininos, para dupla proteção</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Primário</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Consiste na aquisição/compra e oferta de preservativos femininos para a dupla protecção</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2012?</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA/Fundo Global</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -3146,17 +3391,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saúde Infantil</t>
+          <t>Planeamento Familiar</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Manejo da criança dos 0-59 meses com pneumonia</t>
+          <t xml:space="preserve">Oferta de Levonorgestrel 75mg-Pílula de dia Seguinte </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3166,40 +3411,26 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administração de Amoxicilina Trihidrato; 250mg/5ml, suspensão oral, em crianças dos 0-59 meses </t>
+          <t>Consiste na aquisição/compra e oferta de pílula do dia Seguinte</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>MISAU</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>770.246</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>836.976</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>108.0%</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0.45 (USD)</t>
-        </is>
-      </c>
+          <t>UNFPAUNFPA/Fundo Global</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -3220,17 +3451,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Saúde Infantil</t>
+          <t>Planeamento Familiar</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
+          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Manejo da criança dos 0-59 meses com disenteria</t>
+          <t>Oferta de Contrcepção nos SAAJ-Serviços Amigos dos Adolescente se Jovens</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -3240,40 +3471,20 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administração de Ciprofloxacina (comp. 250mg ou 500mg) 15mg/kg/2x ao dia, durante 3 dias, em crianças dos 0-59 meses </t>
+          <t xml:space="preserve">Consiste na aquisição/compra e oferta de contraceptivos </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>MISAU</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>47.094</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>46.107</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>98.0%</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>0.46 (USD)</t>
-        </is>
-      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -3289,22 +3500,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saúde Infantil</t>
+          <t>Planeamento Familiar</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
+          <t xml:space="preserve">Oferta de Contracepção/PF baseado na escolha informada nas Consultas Integradas </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Manejo da criança dos 0-59 meses com malária</t>
+          <t>Integração de  PF nos outros serviços</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3314,37 +3525,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administração de Antimaláricos em crianças dos 0-59 meses</t>
+          <t>Oferta de Contracepção/Planeamento Familiar na Brigada Móvel, Pós-Parto CCS, CCR, CCD, PAV;  Triagem de Adultos, Cuidados e tratamento de HIV e outras consultas externas</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>3.012.380</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>3.008.269</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>99.9%</t>
-        </is>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="e">
+        <v>#DIV/0!</v>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Gestão de Antimaláricos e outros insumos, ao nível do programa da Malária</t>
-        </is>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_41.html</t>
@@ -3359,75 +3564,56 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Saúde Infantil</t>
+          <t>Planeamento Familiar</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Atenção integrada as doenças da infância (AIDI/CCD)</t>
+          <t>Oferta de Contracepção/PF através dos APS  a nível da Comunidade</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Aquisição dos cantinhos de rehidratação oral, para tratamento oportuno da desidratação em crianças dos 0-59 meses</t>
+          <t>PF na comunidade através de APS</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Comunitário</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Consiste na aquisição e disponibilização de copos plásticos, bacia plástica, tabuleiros e jarros coloridos que compõem o Cantinho de Reidratação Oral, com o objectivo de prevenir e reduzir a morbi-mortalidade por diarreias.</t>
+          <t xml:space="preserve">Oferta de Contracepção/Planeamento Familiar pelo APS na comunidade onde ele trabalha </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a mortalidade infantil</t>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>UNICEF
- Alcançar/FHI 360</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>260.077</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>25 (USD)</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>Não temos como obter quantas crianças com diarreia foram hidratadas</t>
-        </is>
-      </c>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_42.html</t>
@@ -3442,7 +3628,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3452,12 +3638,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t>Oferta de PF Pós-Parto Imediato</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Contraceptivos orais combinados -  Microgynon (Etinilestradiol 0.03mg+0.15mg),comprimidos </t>
+          <t xml:space="preserve">Oferta PF Pós parto </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3467,28 +3653,28 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consiste na aquisição/compra de Microgynon (Etinilestradiol 0.03mg+0.15mg), ciclos  </t>
+          <t>Oferta de PF no Pós-Parto Imediato, na Maternidade dentro das 48 horas após o parto</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>MIF's= 8159149</t>
-        </is>
-      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Casal Ano Protegido= 361599</t>
+          <t>DIU pós-parto =92540</t>
         </is>
       </c>
       <c r="M44" s="2" t="e">
@@ -3510,7 +3696,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3520,12 +3706,12 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t>Oferta de PF Pós-Aborto</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Contraceptivos orais só com progesterona -  Microgynon (Etinilestradiol 0.03mg+0.15mg),comprimidos </t>
+          <t>Oferta de PF na Urgência de Ginecologia</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -3535,15 +3721,19 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Aquisição e distribuição de Microlut( Levonorgestrel 30mcg), ciclos</t>
+          <t xml:space="preserve">Oferta de PF na urgência de Ginecologia, para as utentes no Pós - Aborto </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr"/>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>USAID/UNFPA</t>
@@ -3570,7 +3760,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3580,32 +3770,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t>Auto-injecção</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Sayana Press 104mg/0.65mg, injectavel, incluindo Auto - Injeção</t>
+          <t>Auto-injecção com DMPA-SC- acetato de medroxiprogesterona (Sayana Press)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Comunitário</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Aquisição de Sayana Press 104mg/0.65mg, injectavel</t>
+          <t xml:space="preserve">Oferta de Auto - Injecção com Sayana Press </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3614,13 +3804,9 @@
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Casal Ano Protegido = 1234207</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="e">
-        <v>#VALUE!</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
@@ -3638,52 +3824,74 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Depo-Provera(Medroxiprogesterona 150mg/ml), injectavel</t>
+          <t xml:space="preserve">Planificação das necessidades dos suplementos e medicamentos para o tratamento da desnutrição aguda  </t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Aquisição de Depo-Provera(Medroxiprogesterona 150mg/ml), injectavel</t>
+          <t xml:space="preserve">Planificação da compra das necessidades Anuais para os LT, ATPU , ASPU para crianças  que venham desenvolver a desnutrição aguda, incluindo equipamentos antropometricos para o seu diagnostico </t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
+          <t xml:space="preserve">reduzir a morbimortalidade infantil, o baixo peso a nascencia </t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr"/>
+          <t>Banco Mundial, UNICEF e WFP</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>5.262.815</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>192.567</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>175.18</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exercicio de planificação para responder a toda a demanda do programa quer em ensumos, materiais como a monitoria e desempenho </t>
+        </is>
+      </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_46.html</t>
@@ -3698,51 +3906,69 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Levoplant 75mg, implante</t>
+          <t xml:space="preserve">Reprodução dos Instrumentos  registo e material de apoio  </t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t xml:space="preserve">Comunitario, Primario, Secundario </t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Aquisição de Levoplant 75mg, implante</t>
+          <t>Disponibilizar  balanças, livros de registo, livro para  o diagnostico do tipo de desnutrição ou baixo peso  para a idade  a todas unidades sanitarias e omunidade</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Monitoria do desempenho e qualidade dos dados da intervenção e  oferta de serviços de saúde/ prestação de cuidados adequados para a redução do risco de letalidade por desnutrição aguda </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -3758,59 +3984,69 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Jadelle (Levonorgestrel 2*75mg), implante</t>
+          <t xml:space="preserve"> Analise  de dados e retro-informação trimestral </t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Aquisição de Jadelle (Levonorgestrel 2*75mg), implante</t>
+          <t xml:space="preserve">Analise  do desepenho em termos de crianças identificadas com Desnutrição aguda, e o Desempenho do programa </t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr"/>
+          <t xml:space="preserve">Garantir o uso sistemático dos dados para a tomada de decisão, por meio da análise periódica da informação recolhida, permitindo avaliar o desempenho das intervenções, identificar lacunas, tendências e oportunidades de melhoria, e fornecer retro-informação atempada aos níveis envolvidos, de forma a ajustar estratégias, reforçar a qualidade da implementação e melhorar os resultados programáticos. </t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
+          <t>HKI</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>8.159.149</t>
+          <t>Profissionais de Saude</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Casal Ano Protegido= 2650599</t>
-        </is>
-      </c>
-      <c r="M49" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N49" s="3" t="inlineStr"/>
+          <t xml:space="preserve">3 provincias </t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>12 Distritos</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Nampula-10048 USD                      Sofala- 9762 USD                    Zambezia- 10048 USD</t>
+        </is>
+      </c>
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -3826,55 +4062,69 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>vigilancia nutricional</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Monitoria do crescimento, desenvolvimento  e do estado nutricional de crianças, Adolescente, </t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Implanon (Etonogestrel 68mg),implante</t>
+          <t xml:space="preserve">Monitoria do crescimento e desenvolvimento infantil, </t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Aquisição de Implanon (Etonogestrel 68mg), Implante</t>
+          <t>Monitoria dos marcos do desenvolvimento para a idade,  monitoria da curva do peso  em relacao a estatura para o diagnostico da Desnutrição crónica e da desnutrição aguda</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Contribuir para o Desenvolvimento da Primeira Infancia,  observando se as crianças estão a crescer bem mas também se desenvolvem de acordo com a faixa ectária </t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>5.262.815</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Casal Ano Protegido= 335980</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>8.962.806</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>$ 25,95</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -3890,55 +4140,69 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Monitoria  do estado nutricional de   MGL, G, ML, TARV e TB  e Adultos no geral  </t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Copper T380 0.2%, DIU</t>
+          <t xml:space="preserve">Rastreio da Desnutrição aguda  MG, G, ML, TARV e TB </t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Aquisição de Copper T380 0.2%, DIU</t>
+          <t>Oferta de  ATPU  e educacao Nutricional a  MG, ML, TARV e TB    para o tratamento da DAG com complicacoes medicas</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr"/>
+          <t>Prevenir a desnutrição  aguda, reduzir mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>1662221  de MG</t>
+        </is>
+      </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Casal Ano Protegido= 974344</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N51" s="3" t="inlineStr"/>
+          <t>1.783.098</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0,033</t>
+        </is>
+      </c>
       <c r="O51" s="3" t="inlineStr"/>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -3954,56 +4218,74 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t xml:space="preserve">Tratamento da desnutrição aguda </t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Preservativos masculinos, para dupla proteção</t>
+          <t>Tratamento da Desnutrição aguda  Grave com  complicações médicas com os leites Terapêuticos  (F100 e F75), ATPU  - crianças dos 6-59 meses</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t xml:space="preserve">Primario, secundário e Terciario </t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Aquisição e distribuição de preservativos masculinos para a dupla protecção</t>
+          <t>Oferta de leites Terapêuticos  (F100 e F75), ATPU a  crianças dos 6-59 meses para o tratamento da DAG com complicacoes medicas</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t>Prevenir a desnutrição  aguda, reduzir mortalidade infantil</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>12.568</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>12.568</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tratamento nutricional  a crianças com Desnutrição aguda  </t>
+        </is>
+      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_51.html</t>
@@ -4018,51 +4300,69 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva,  Mulher e Criança</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF baseado na escolha informada e até a última milha</t>
+          <t>Tratamento da desnutrição aguda</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Levonorgestrel 75mg-Pílula de dia Seguinte </t>
+          <t>Tratamento de Desnutrição aguda Grave sem complicações médicas com o ATPU a criancas dos 6-59 meses</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Aquisição e distribuição de pílula do dia Seguinte</t>
+          <t>Oferta de ATPU a  crianças dos 6-59 meses para o tratamento da DAG sem  complicacoes medicas</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
+          <t>tratar crianças com desnutrição aguda</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>UNFPA</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N53" s="3" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>106.966</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>133.439</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>$ 0,33</t>
+        </is>
+      </c>
       <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -4083,50 +4383,64 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t>Programa de Reabilitação Nutricional</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Contracepção/PF baseado na escolha informada nas Consultas Integradas </t>
+          <t>Programa de Suplementação Nutricional criancas dos 6-59 meses</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Integração de  PF nos outros serviços</t>
+          <t>Programa de Suplementação com ASPU para a Desnutrição aguda Moderada e prevenção da evolução para a forma mais grave em crianças dos 6-59 meses</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/Planeamento Familiar na Brigada Móvel, CCS, CCR, CCD, PAV;  Triagem de  de Adultos, Cuidados e tratamento de HIV</t>
+          <t>Oferta de ASPU a  crianças dos 6-59 meses para o tratamento da DAG sem  complicacoes medicas</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t xml:space="preserve">suplementar com ASPU  as crianças com desnutrição aguda moderada </t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>85.573</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>78.636</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>91.9%</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>$ 0,33</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
@@ -4147,51 +4461,69 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Oferta de Contracepção/PF através dos APS  a nível da Comunidade</t>
+          <t xml:space="preserve">Suplementação com Ferro e ácido Fólico a raparigada adolescente e a MGL </t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>PF na comunidade através de APS</t>
+          <t xml:space="preserve">Aquisição e  oferta de Ferro e acido fólico de 90+1e oferta a mulher gravida, lactante e adolescente para a prevenção da anemia  e malformações congenitas </t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Comunitário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Contracepção/Planeamento Familiar pelo APS na comunidade onde ele trabalha </t>
+          <t>Oferta de Ferro e acido fólico de 60+0.4 e oferta a mulher gravida, lactante para a prevenção da anemia  e malformações congenitas</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t xml:space="preserve">Prevenção da anemia  na Mulher grávida e complicações no parto </t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>Inicio  em 2002,</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>3.158.220</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>2.744.268</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>86.9%</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>Suplementação com duas doses anuais de vitamina A as crianças dos 6-59 meses</t>
+        </is>
+      </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_54.html</t>
@@ -4211,54 +4543,64 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Oferta de PF Pós-Parto Imediato</t>
+          <t>Suplementação com Ferro e ácido Fólico a raparigada adolescente</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta PF Pós parto </t>
+          <t xml:space="preserve">Aquisição e  oferta de Ferro e acido fólico de 60+40 mg e oferta a rapariga adolescente para a prevenção da anemia  e malformações congenitas </t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Oferta de PF no Pós-Parto Imediato, na Maternidade</t>
+          <t>de Ferro e acido fólico de 60+0.4 e oferta a  adolescente para a prevenção da anemia  e malformações congenitas</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t xml:space="preserve">Prevenção da anemia  na adolescente </t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>4.364.555</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>DIU pós-parto =92540</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>1.979.052</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>45.3%</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4274,55 +4616,69 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t xml:space="preserve">Saúde reprodutiva, Mulher, crianças eNutrição </t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Oferta de PF Pós-Aborto</t>
+          <t xml:space="preserve">Desparasitação  de Crianças dos 12-59 meses </t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Oferta de PF na Urgência de Ginecologia</t>
+          <t>Aquisição e oferta de Mebendazol de  500 mg ou Albendazol de 400 mg</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Primário</t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de PF na urgência de Ginecologia, para as utentes no Pós - Aborto </t>
+          <t xml:space="preserve">Desparasitar todas as criancas dos 12-59 meses com Mebendazol ou Albendazol </t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N57" s="3" t="inlineStr"/>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>4.124.130</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>3.803.415</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>92.2%</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>$ 0,033</t>
+        </is>
+      </c>
       <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -4338,53 +4694,55 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t xml:space="preserve">Saúde Reprodutiva, Mulher e Criança </t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Planeamento Familiar</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Auto-injecção</t>
+          <t xml:space="preserve">Desparasitacao da Mulher Gravida </t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Auto-injecção com acetato de medroxiprogesterona (Sayana Press)</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Comunitário</t>
-        </is>
-      </c>
+          <t>Aquisição e oferta de Mebendazol de  500 mg ou Albendazol de 400 mg</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Auto - Injeção por Sayana Press </t>
+          <t>Desparasita toda a mulher grávida</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejado</t>
+          <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="e">
-        <v>#DIV/0!</v>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>1.662.221</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>1.783.090</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>107.3%</t>
+        </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
@@ -4402,74 +4760,66 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
+          <t>Suplementação com micronutriente em Pó as crianças dos 6-23meses</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planificação das necessidades dos suplementos e medicamentos para o tratamento da desnutrição aguda  </t>
+          <t xml:space="preserve">Aquisição, compra e distribuição  do Micronutriente em pó para a prevenção da desnutrição crónica </t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Primario</t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planificação da compra das necessidades Anuais para os LT, ATPU , ASPU para crianças  que venham desenvolver a desnutrição aguda, incluindo equipamentos antropometricos para o seu diagnostico </t>
+          <t>Suplimentar com MNP</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">reduzir a morbimortalidade infantil, o baixo peso a nascencia </t>
+          <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Banco Mundial, UNICEF e WFP</t>
+          <t xml:space="preserve">BANCO Mundal </t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>5.262.815</t>
+          <t>2.224.037</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>192.567</t>
+          <t>1.688.331</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>175.18</t>
-        </is>
-      </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Exercicio de planificação para responder a toda a demanda do programa quer em ensumos, materiais como   a monitoria e desempenho </t>
-        </is>
-      </c>
+          <t>75.9%</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_58.html</t>
@@ -4484,69 +4834,45 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
+          <t>Suplementação com micronutriente em Pó as crianças dos 6-23meses</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reprodução dos Instrumentos  registo e material de apoio  </t>
+          <t xml:space="preserve">Oferta do Micronutriente em pó na Unidade Sanitária e comunidade as crianças dos 6-23 meses  para a  prevenção da desnutrição crónica </t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comunitario, Primario, Secundario </t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Disponibilizar  balanças, livros de registo, livro para  o diagnostico do tipo de desnutrição ou baixo peso  para a idade  a todas unidades sanitarias e omunidade</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Primario e Comunitario </t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoria do desempenho e qualidade dos dados da intervenção e  oferta de serviços de saúde/ prestação de cuidados adequados para a redução do risco de letalidade por desnutrição aguda </t>
+          <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
@@ -4562,22 +4888,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planificação Lógistica e Monitoria e Avaliação </t>
+          <t xml:space="preserve">Suplementação com Vitamina A  </t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Analise  de dados e retro-informação trimestral </t>
+          <t xml:space="preserve">Aquisição, compra e oferta de capsulas de Vitamina A de 100. 000 ui a crianças dos 6-11 meses para a prevenção da deficiência de Vitamina A e cegueira noturnal </t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -4587,44 +4913,40 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analise  do desepenho em termos de crianças identificadas com Desnutrição aguda, e o Desempenho do programa </t>
+          <t>Suplementar todas as crianças dos 6-11 meses com 1 dose de Vitamina A</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garantir o uso sistemático dos dados para a tomada de decisão, por meio da análise periódica da informação recolhida, permitindo avaliar o desempenho das intervenções, identificar lacunas, tendências e oportunidades de melhoria, e fornecer retro-informação atempada aos níveis envolvidos, de forma a ajustar estratégias, reforçar a qualidade da implementação e melhorar os resultados programáticos. </t>
+          <t>Prevenção da deficiencia de vitaminaA - Segueria  Notura  - redução dos actuais 64%</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>HKI</t>
+          <t>Banco Mundial, UNICEF</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Profissionais de Saude</t>
+          <t>1.138.685</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 provincias </t>
+          <t>1.599.356</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>12 Distritos</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>Nampula-10048 USD                      Sofala- 9762 USD                    Zambezia- 10048 USD</t>
-        </is>
-      </c>
+          <t>140.5%</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr"/>
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -4640,22 +4962,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoria do crescimento, desenvolvimento  e do estado nutricional de crianças, Adolescente, MGL, Adultos no geral  </t>
+          <t xml:space="preserve">Suplementação com Vitamina A  </t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoria do crescimento e desenvolvimento infantil, </t>
+          <t xml:space="preserve">Aquisição, compra e oferta de capsulas de Vitamina A de 200. 000 ui a crianças dos 12-59 meses para a prevenção da deficiência de Vitamina A, cegueira noturnal  e reforço do  sistema imunologico </t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4665,44 +4987,40 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Monitoria dos marcos do desenvolvimento para a idade,  monitoria da curva do peso  em relacao a estatura para o diagnostico da Desnutrição crónica e da desnutrição aguda</t>
+          <t>Suplementar todas as crianças dos 12- 59 meses com 2 doses de Vitamina A</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contribuir para o Desenvolvimento da Primeira Infancia,  observando se as crianças estão a crescer bem mas também se desenvolvem de acordo com a faixa ectária </t>
+          <t>Prevenção da deficiência de micronutrientes e assim redução da DC</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>UNICEF</t>
+          <t>Banco Mundial, UNICEF</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5.262.815</t>
+          <t>4.124.130</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>8.962.806</t>
+          <t>2.624.187</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>$ 25,95</t>
-        </is>
-      </c>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -4718,65 +5036,53 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Pacote de Intervenções de Nutrição na comunidade </t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoria  do estado nutricional de crianças,  MGL, Adultos no geral  </t>
+          <t xml:space="preserve">Oferta do pacote de Intervenções de nutrição  completo de acordo com a faixa ectária  as crianças dos 6-23 meses </t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Rastreio da Desnutrição aguda  MG</t>
+          <t xml:space="preserve">Prestação de serviços de nutrição  na comunidade com foco em crianças dos 6-23 meses: </t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
+          <t>Comunitario</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Oferta de um conjunto de 7 intervenções essenciais voltadas as crianças dos 6-23 meses</t>
+        </is>
+      </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>Prevenir a desnutrição  aguda, reduzir mortalidade infantil</t>
+          <t>Redução da Desnutrição crónica, desnutrição aguda   e deficiência de micronutrientes  e melhoria das praticas de nutricao na comunidade  a partir de uma intervenção de elevado impacto com foco nos 1000 dias</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>1662221  de MG</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>1.783.098</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 0,033</t>
-        </is>
-      </c>
+          <t>Banco Mundial, UNICEF</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -4792,37 +5098,37 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t>Educação Alimentar</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Tratamento da desnutrição aguda</t>
+          <t xml:space="preserve">Promoção </t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tratamento da Desnutrição aguda  Grave com  complicações médicas com os leites Terapêuticos  (F100 e F75), ATPU  - crianças dos 6-59 meses</t>
+          <t>Educação para a saúde  em relação a conservação e uso dos alimentos localmente disponíveis e preparacao de refeicoes nutricionais balaceadas</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario, secundário e Terciario </t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Oferta de leites Terapêuticos  (F100 e F75), ATPU a  crianças dos 6-59 meses para o tratamento da DAG com complicacoes medicas</t>
+          <t>Sessao de educacao nutricional aos pacientes em tratamento da desnutricao aguda</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Prevenir a desnutrição  aguda, reduzir mortalidade infantil</t>
+          <t xml:space="preserve">Redução da desnutrição crónica, desnutrição aguda   e deficiência de micronutrientes a partir da promoção  de conhecimento e competencias das familias e cuidadores para o uso adequado, seguro e nutricionalmente correcto dos alimentos localmente diponiveis  de modo a melhorar a qualidade da alimentação infantil e combater os tabus associados a alimentação infantil e da mulher gravida e lactante </t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4832,34 +5138,26 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>UNICEF</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>12.568</t>
+          <t>106.966</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>12.568</t>
+          <t>42.184</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Tratamento nutricional  a crianças com Desnutrição aguda  </t>
-        </is>
-      </c>
+          <t>39.4%</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_63.html</t>
@@ -4874,37 +5172,37 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t>Educação Alimentar</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Tratamento da desnutrição aguda</t>
+          <t xml:space="preserve">Promoção </t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Tratamento de Desnutrição aguda Grave sem complicações médicas com o ATPU a criancas dos 6-59 meses</t>
+          <t>Aconselhamento em relação as práticas de higiene,conservação   e escolha do alimentos  par</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Primario</t>
+          <t xml:space="preserve">Primario e Comunitario </t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Oferta de ATPU a  crianças dos 6-59 meses para o tratamento da DAG sem  complicacoes medicas</t>
+          <t xml:space="preserve">Palestras, sessões de aconselhamento </t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>tratar crianças com desnutrição aguda</t>
+          <t xml:space="preserve">Redução da Desnutrição crónica. Reforçar mudanças de comportamento junto de pais, cuidadores e famílias, promovendo práticas adequadas de higiene alimentar, conservação segura e selecção de alimentos saudáveis, com vista à prevenção de doenças transmitidas por alimentos, melhoria da qualidade da dieta e protecção da saúde das crianças, especialmente nos primeiros dois anos de vida. </t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -4914,7 +5212,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>UNICEF</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -4924,19 +5222,15 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>133.439</t>
+          <t>151.107</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>$ 0,33</t>
-        </is>
-      </c>
+          <t>141.3%</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -4952,22 +5246,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Promocao e proteccao ao Aleitamento Materno </t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Tratamento da desnutrição aguda</t>
+          <t>Proteccao e insentivo ao aleitamento materno exclusivo dos 0 aos 6 meses</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>tratamento a desnutricao aguda MGL, TB, HIV</t>
+          <t xml:space="preserve">Monitoria do Codigo de comercialização dos substituos do Leite maternos </t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4977,44 +5271,24 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Usar suplementos como CSB + para o tratamento</t>
+          <t>Monitoria para o seguimento do CCSLM para a promoção e incentivo ao Aleitamento amterno</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tratar MGL, TB e Pacientes HIV   com desnutrição para melhoria do seu estado nutricional e melhor prognostico no tratamento  bem como  redução do baixo peso ao nascer ou complicações no parto e pos parto para MG </t>
+          <t>Assegurar o cumprimento do Código Internacional de Comercialização dos Substitutos do Leite Materno, prevenindo práticas de promoção inadequadas que possam interferir com o aleitamento materno, e protegendo, promovendo e apoiando o aleitamento materno exclusivo até aos 6 meses e continuado até aos 2 anos ou mais.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>59.128</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
@@ -5030,22 +5304,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Programa de Reabilitação Nutricional</t>
+          <t xml:space="preserve">Promocao e proteccao ao Aleitamento Materno </t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Programa de Suplementação Nutricional criancas dos 6-59 meses</t>
+          <t>Proteccao e insentivo ao aleitamento materno exclusivo dos 0 aos 6 meses</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Programa de Suplementação para a Desnutrição aguda Moderada e prevenção da evolução para a forma mais grave em crianças dos 6-59 meses</t>
+          <t xml:space="preserve">Monitoria do Codigo de comercialização dos substituos do Leite maternos </t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -5055,12 +5329,12 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Oferta de ASPU a  crianças dos 6-59 meses para o tratamento da DAG sem  complicacoes medicas</t>
+          <t>Monitoria para o seguimento do CCSLM para a promoção e incentivo ao Aleitamento amterno</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">suplementar com ASPU  as crianças com desnutrição aguda moderada </t>
+          <t>Assegurar o cumprimento do Código Internacional de Comercialização dos Substitutos do Leite Materno, prevenindo práticas de promoção inadequadas que possam interferir com o aleitamento materno, e protegendo, promovendo e apoiando o aleitamento materno exclusivo até aos 6 meses e continuado até aos 2 anos ou mais.</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -5068,31 +5342,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>85.573</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>78.636</t>
-        </is>
-      </c>
-      <c r="M67" s="3" t="inlineStr">
-        <is>
-          <t>91.9%</t>
-        </is>
-      </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
-          <t>$ 0,33</t>
-        </is>
-      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -5108,22 +5362,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Saúde Reprodutiva,  Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suplementação com Ferro e ácido Fólico a raparigada adolescente e a MGL </t>
+          <t>Logistica de Vacinas</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição e  oferta de Ferro e acido fólico de 60+0.4 e oferta a mulher gravida, lactante e adolescente para a prevenção da anemia  e malformações congenitas </t>
+          <t>Implementar o Plano de Distribuição regular de vacinas e material de vacinação</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -5133,49 +5387,25 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Ferro e acido fólico de 60+0.4 e oferta a mulher gravida, lactante para a prevenção da anemia  e malformações congenitas</t>
+          <t>Lançamento de concurso, assinatura de contrato com fornecidor, Requisição de serviço pela Logística, carregamento dos camiões no armazém nacional para os regionais, intermediários e provinciais e recepção e verificação da quelidade do produto.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção da anemia  na Mulher grávida e complicações no parto </t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Inicio  em 2002,</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3.158.220</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>2.744.268</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>86.9%</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Suplementação com duas doses anuais de vitamina A as crianças dos 6-59 meses</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_67.html</t>
@@ -5190,69 +5420,49 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saúde reprodutiva, Mulher, crianças eNutrição </t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desparasitação  de Crianças dos 12-59 meses </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição e oferta de Mebendazol de  500 mg ou Albendazol de 400 mg a </t>
+          <t xml:space="preserve">Implementar brigadas móveis </t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
+          <t>Comunitario</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desparasitar todas as criancas dos 12-59 meses com Mebendazol ou Albendazol </t>
+          <t>Mapeamento de pontos de concentração por áreas de saúde, replanificação com os líderes comunitários (estimativas de grupos alvos e consumíveis), Aprovação do plano de brigadas móveis e envio de recursos financeiros às provincias e execussão do plano.</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>4.124.130</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>3.803.415</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>92.2%</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>$ 0,033</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -5268,52 +5478,48 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saúde Reprodutiva, Mulher e Criança </t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desparasitacao da Mulher Gravida </t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição e oferta de Mebendazol de  500 mg ou Albendazol de 400 mg a </t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+          <t>Realizar visitas de supervisão integrada e apoio técnico em monitoria das actividades do PAV, logística, vigilância e RED/REC</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Primario</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Mapeamento e identificação dos principais indicadores com desafios de qualidade e cumprimento de metes, acesso e apropriação do plano de implementação das diferentes intervenções das áreas do programa, elaboração do plano de seguimento (monitoria), aprovação do plano e sua implementação.</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1.662.221</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>1.783.090</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>107.3%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr"/>
       <c r="P70" s="2" t="inlineStr">
@@ -5330,60 +5536,49 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Saúde reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Suplementação com micronutriente em Pó as crianças dos 6-23meses</t>
+          <t>Comunicação e Demanda</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição, compra e distribuição  do Micronutriente em pó para a prevenção da desnutrição crónica </t>
+          <t>Produzir e fazer inserção de spots de rádio e de TV sobre vacinação de rotina</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
+          <t>Comunitario</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Produção dos Spots de acordo as mensagens que pretende passar, tradução dos spots radiofonicos em linguas necessárias, inserção dos spots produzidos.
+Spots televisivos -  instrção a televisão (Nacional).</t>
+        </is>
+      </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BANCO Mundal </t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2.224.037</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>1.688.331</t>
-        </is>
-      </c>
-      <c r="M71" s="3" t="inlineStr">
-        <is>
-          <t>75.9%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="inlineStr">
@@ -5405,37 +5600,45 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Suplementação com micronutriente em Pó as crianças dos 6-23meses</t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta do Micronutriente em pó na Unidade Sanitária e comunidade as crianças dos 6-23 meses  par aa prevenção da desnutrição crónica </t>
+          <t>Introduzir novas vacinas na rotina (Ex: Vacina contra Hepatite B a nascença)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
+          <t>Primario</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Elaboração do Palno de Aplicação da Vacina no País para a sua aproção pela GAVI, Elaboração do Microplano (mapeamento do grupo alvo, estimativa de recursos necessários), Emissão de nota comunicativa sobre a introdução da vacina do mais alto nivel até a base, Lançamento da Introdução da vacina, Sua implementação.</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
+          <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>2.270.553</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr"/>
@@ -5454,64 +5657,52 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Saúde reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suplementação com Vitamina A  </t>
+          <t>Prestação de Serviços</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição, compra e oferta de capsulas de Vitamina A de 100. 000 ui a crianças dos 6-11 meses para a prevenção da deficiência de Vitamina A e cegueira noturnal </t>
+          <t>Expandir a vacinação contra Malária para 8 provincias</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
+          <t>Primário</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Suplementar todas as crianças dos 6-11 meses com 1 dose de Vitamina A</t>
+          <t xml:space="preserve"> Elaboração do Microplano (mapeamento do grupo alvo, estimativa de recursos necessários), Envio às provincias para efeitos de correção, actualização e validação, Emissão de nota comunicativa sobre a introdução da vacina do mais alto nivel até a base, Lançamento da Introdução da vacina na Província, sua implementação.</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Prevenção da deficiencia de vitaminaA - Segueria  Notura  - redução dos actuais 64%</t>
+          <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>Banco Mundial, UNICEF</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>1.138.685</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>1.599.356</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>140.5%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="inlineStr">
@@ -5528,64 +5719,48 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Saúde reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevenção de Deficiência de Micronutrientes </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suplementação com Vitamina A  </t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aquisição, compra e oferta de capsulas de Vitamina A de 200. 000 ui a crianças dos 12-59 meses para a prevenção da deficiência de Vitamina A, cegueira noturnal  e reforço do  sistema imunologico </t>
+          <t>Pagar o co-financiamento da vacina contra Rotavírus, PCV13, DTPHepBHib, MR2 e IPV</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Suplementar todas as crianças dos 12- 59 meses com 2 doses de Vitamina A</t>
+          <t>Faz-se a quantificação da vacina, Solicitação da estimativa de custo, canalizar o processo para a DAF para todo o prcedimento para o pagamento (suportado pelo Orçamento do Estado)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Prevenção da deficiência de micronutrientes e assim redução da DC</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Banco Mundial, UNICEF</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4.124.130</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>2.624.187</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
@@ -5602,50 +5777,46 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Saúde reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pacote de Intervenções de Nutrição na comunidade </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta do pacote de Intervenções de nutrição  completo de acordo com a faixa ectária  as crianças dos 6-23 meses </t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Prestação de serviços de nutrição  na comunidade com foco em crianças dos 6-23 meses: Aconselhamento em aleitamento materno exclusivo, alimentação complementar adequada e Higiene e saneamento do Meio,  Monitoria do crescimento p/I; suplementação com Vitamina A  e Micronutriente em pó dos 6-23 meses e Desparasitação. Para o alcance de crianças com o PIN completo e prevenção de todas as formas de desnutrição (Desnutrição aguda, crónica e deficiência de Micronutrientes)</t>
+          <t>Pagar o co-financiamento do CCEOP (502 geleiras)</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Comunitario</t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Oferta de um conjunto de 7 intervenções essenciais voltadas as crianças dos 6-23 meses</t>
+          <t>Fazer o levantamento de necessidades de equipamentos da cadeia de frio, solicitação de financiamento para aquisção da parte da GAVI, Distribuição dos equipamentos de acordo com o as necessidades levantadas.</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>Redução da Desnutrição crónica, desnutrição aguda   e deficiência de micronutrientes  e melhoria das praticas de nutricao na comunidade  a partir de uma intervenção de elevado impacto com foco nos 1000 dias</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>Banco Mundial, UNICEF</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>2.270.553</t>
+        </is>
+      </c>
       <c r="L75" s="3" t="inlineStr"/>
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="3" t="inlineStr"/>
@@ -5664,64 +5835,52 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Saúde reprodutiva, Mulher e Criança</t>
+          <t>Saúde Reprodutiva, Mulher e Criança</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demonstrações Culinárias </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promoção </t>
+          <t>Gestão</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Educação para a saúde  em relação a conservação e uso dos alimentos localmente disponíveis </t>
+          <t>Aquisição de 296 motorizadas</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
+          <t>Comunitario</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Sessao de educacao nutricional aos pacientes em tratamento da desnutricao aguda</t>
+          <t>Fazer o levantamento de necessidades, inclusão ao orçamento do HSS 2025, aquisição pela UNICEF e fazer a distribuição de acordo com as necessidades levantadas.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redução da desnutrição crónica, desnutrição aguda   e deficiência de micronutrientes a partir da promoção  de conhecimento e competencias das familias e cuidadores para o uso adequado, seguro e nutricionalmente correcto dos alimentos localmente diponiveis  de modo a melhorar a qualidade da alimentação infantil e combater os tabus associados a alimentação infantil e da mulher gravida e lactante </t>
+          <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>OE</t>
-        </is>
-      </c>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>106.966</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>42.184</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>39.4%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr"/>
       <c r="P76" s="2" t="inlineStr">
@@ -5743,59 +5902,43 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Educação Alimentar</t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promoção </t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Aconselhamento em relação as práticas de higiene,conservação   e escolha do alimentos  par</t>
+          <t>Reprodução de instrumentos de registo</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primario e Comunitario </t>
+          <t>Primario</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palestras, sessões de aconselhamento </t>
+          <t>Estimativa de necessidade dos instrumentos (livros, fichas, Cartões), Lançamento de concurso para reprodução de instrumentos, Reprodução do material, elaboração de plano de distribuição de intrumentos e sua implementação.</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Redução da Desnutrição crónica. Reforçar mudanças de comportamento junto de pais, cuidadores e famílias, promovendo práticas adequadas de higiene alimentar, conservação segura e selecção de alimentos saudáveis, com vista à prevenção de doenças transmitidas por alimentos, melhoria da qualidade da dieta e protecção da saúde das crianças, especialmente nos primeiros dois anos de vida. </t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>OE</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>106.966</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>151.107</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>141.3%</t>
-        </is>
-      </c>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr">
@@ -5817,17 +5960,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promocao e proteccao ao Aleitamento Materno </t>
+          <t>PAV</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Proteccao e insentivo ao aleitamento materno exclusivo dos 0 aos 6 meses</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoria do Codigo de comercialização dos substituos do Leite maternos </t>
+          <t>Planificação anual das actividades do PAV (Nacional, Provincial e Distrital)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5837,21 +5980,21 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Monitoria para o seguimento do CCSLM para a promoção e incentivo ao Aleitamento amterno</t>
+          <t>Revisão da metodologia para a planificação, inicia o processo de planificação a partir dos distritos com as unidades sanitárias, realizar a reunião provincial para harmonização e agregação dos planos distritais, processo de planificação do nivcel central e realização da reunião de planificação nacional.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Assegurar o cumprimento do Código Internacional de Comercialização dos Substitutos do Leite Materno, prevenindo práticas de promoção inadequadas que possam interferir com o aleitamento materno, e protegendo, promovendo e apoiando o aleitamento materno exclusivo até aos 6 meses e continuado até aos 2 anos ou mais.</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
+          <t>Reduzir a morbi-mortalidade infantil</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>2.270.553</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr"/>
@@ -5862,657 +6005,6 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>smi_78</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Logistica de Vacinas</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>Implementar o Plano de Distribuição regular de vacinas e material de vacinação</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>Lançamento de concurso, assinatura de contrato com fornecidor, Requisição de serviço pela Logística, carregamento dos camiões no armazém nacional para os regionais, intermediários e provinciais e recepção e verificação da quelidade do produto.</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr"/>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="3" t="inlineStr"/>
-      <c r="N79" s="3" t="inlineStr"/>
-      <c r="O79" s="3" t="inlineStr"/>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_78.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>smi_79</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Implementar brigadas móveis </t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Comunitario</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Mapeamento de pontos de concentração por áreas de saúde, replanificação com os líderes comunitários (estimativas de grupos alvos e consumíveis), Aprovação do plano de brigadas móveis e envio de recursos financeiros às provincias e execussão do plano.</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_79.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>smi_80</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>Realizar visitas de supervisão integrada e apoio técnico em monitoria das actividades do PAV, logística, vigilância e RED/REC</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>Mapeamento e identificação dos principais indicadores com desafios de qualidade e cumprimento de metes, acesso e apropriação do plano de implementação das diferentes intervenções das áreas do programa, elaboração do plano de seguimento (monitoria), aprovação do plano e sua implementação.</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="3" t="inlineStr"/>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="3" t="inlineStr"/>
-      <c r="O81" s="3" t="inlineStr"/>
-      <c r="P81" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_80.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>smi_81</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Comunicação e Demanda</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Produzir e fazer inserção de spots de rádio e de TV sobre vacinação de rotina</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Comunitario</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Produção dos Spots de acordo as mensagens que pretende passar, tradução dos spots radiofonicos em linguas necessárias, inserção dos spots produzidos.
-Spots televisivos -  instrção a televisão (Nacional).</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_81.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>smi_82</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>Introduzir vacina rotina (Ex: Vacina contra Malária)</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Elaboração do Palno de Aplicação da Vacina no País para a sua aproção pela GAVI, Elaboração do Microplano (mapeamento do grupo alvo, estimativa de recursos necessários), Emissão de nota comunicativa sobre a introdução da vacina do mais alto nivel até a base, Lançamento da Introdução da vacina, Sua implementação.</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="inlineStr"/>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr"/>
-      <c r="M83" s="3" t="inlineStr"/>
-      <c r="N83" s="3" t="inlineStr"/>
-      <c r="O83" s="3" t="inlineStr"/>
-      <c r="P83" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_82.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>smi_83</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Prestação de Serviços</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Expandir a vacinação contra Malária para 8 provincias</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Primário</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Elaboração do Microplano (mapeamento do grupo alvo, estimativa de recursos necessários), Envio às provincias para efeitos de correção, actualização e validação, Emissão de nota comunicativa sobre a introdução da vacina do mais alto nivel até a base, Lançamento da Introdução da vacina na Província, sua implementação.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_83.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>smi_84</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>Pagar o co-financiamento da vacina contra Rotavírus, PCV13, DTPHepBHib, MR2 e IPV</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>Faz-se a quantificação da vacina, Solicitação da estimativa de custo, canalizar o processo para a DAF para todo o prcedimento para o pagamento (suportado pelo Orçamento do Estado)</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="3" t="inlineStr"/>
-      <c r="N85" s="3" t="inlineStr"/>
-      <c r="O85" s="3" t="inlineStr"/>
-      <c r="P85" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_84.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>smi_85</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Pagar o co-financiamento do CCEOP (502 geleiras)</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Fazer o levantamento de necessidades de equipamentos da cadeia de frio, solicitação de financiamento para aquisção da parte da GAVI, Distribuição dos equipamentos de acordo com o as necessidades levantadas.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr"/>
-      <c r="P86" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_85.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>smi_86</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Gestão</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>Aquisição de 296 motorizadas</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>Comunitario</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>Fazer o levantamento de necessidades, inclusão ao orçamento do HSS 2025, aquisição pela UNICEF e fazer a distribuição de acordo com as necessidades levantadas.</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="3" t="inlineStr"/>
-      <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr"/>
-      <c r="P87" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_86.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>smi_87</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Reprodução de instrumentos de registo</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Estimativa de necessidade dos instrumentos (livros, fichas, Cartões), Lançamento de concurso para reprodução de instrumentos, Reprodução do material, elaboração de plano de distribuição de intrumentos e sua implementação.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_87.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>smi_88</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Saúde Reprodutiva, Mulher e Criança</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>PAV</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>Planificação anual das actividades do PAV (Nacional, Provincial e Distrital)</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>Primario</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>Revisão da metodologia para a planificação, inicia o processo de planificação a partir dos distritos com as unidades sanitárias, realizar a reunião provincial para harmonização e agregação dos planos distritais, processo de planificação do nivcel central e realização da reunião de planificação nacional.</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a morbi-mortalidade infantil</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
-      <c r="N89" s="3" t="inlineStr"/>
-      <c r="O89" s="3" t="inlineStr"/>
-      <c r="P89" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/smi/smi_88.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/smi/catalogo_SMI.xlsx
+++ b/smi/catalogo_SMI.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,14 +453,20 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -506,40 +512,70 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Alcance geográfico da intervenção</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Recursos necessários para a implementação</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Etapas chave para a implementação</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Riscos e limitações</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Possíveis factores associados aos riscos</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Ano de início</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Gastos em 2024 (USD)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Fonte(s) de financiamento</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Pop. elegível</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Número alcançado</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Custo por unidade</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>URL da Ficha</t>
         </is>
@@ -588,40 +624,70 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Enfermeiras de Saude Materno- Infatil capacitadas  e em número suficiente. Infraestruturas adequadas, ventiladas e iluminadas Disponibilidade de Material, Equipamento e insumos, calendário obstétrico, teste de gravidez, espéculos, ecógrafo e lencois. Médico ou Técnico de Medicina para mentoria e AT às ESMI.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Formacao de formadores em CPN, Formacao de Enfermeiras de SMI no pacote especifico integrado de CPN,  que inclui rastreamento e conduta no Alto Risco Obstetrico.  Infraestrutura adequada_gabinete de CPN com dimensões normais, ventilado, iluminado  e equipado de acordo com as normas. Mentoria e apoio técnico regular_ trimestral. Monitoria e avaliacao  das intervencões_ mensais. Monitoria das profilaxias. Correccão atempada dos "gaps". Visita às PTs e diálogo com as mulheres na comunidade.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade das ESMI, escassez  de RH capacitados sobretudo nas US periféricas, falta de fundos para as mentorias,falta de equipamento (esfigmomanómetro, ecógrafo), medicamentos preventivos e curativos. Falta de actualizacao técnica regular e desmotivacao dos profissionais em todos os escalões, inclusive das ESMI. </t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A falta de infraestrutura adequada, equipamentos, medicamentos e materiais de consumo essenciais, Barreiras geográficas, socioeconômicas e culturais,  Condições de vulnerabilidade social, pobreza, ausência de suporte familiar podem afetar a adesão ao pré-natal.  Barreiras linguísticas ou de compreensão podem dificultar a transmissão de informações importantes às gestantes. Inequidade na distribuicao dos profissionais, sobretudo de ESMI, sobrecarga de trabalho. </t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>1976</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>1.700.000</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>1.292.000</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>76.0%</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Faltam calendário obstétrico, ecógrafo e ESMI capacitadas no cálculo do tempo de gestacao</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_01.html</t>
         </is>
@@ -670,40 +736,70 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Enfermeiras de Saude Materno- Infatil capacitadas , Médico de Clinica Geral e Técnico de medicina em todas as US. Disponibilidade de Material, Equipamento e insumos . Rede de referência e contra-referência funcional.</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Formacao de formadores em CPN, Formacao de Enfermeiras de SMI no pacote integrado especifico de CPN, que inclui ARO, Nutricao e todas as patologias mais comuns na gravidez.  Rastreios sistemático em todas as CPN , tratamento e seguimento. Referência.</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Alta rotatividade do pessoal , baixa motivacao, infraestruturas inadequadas muito pequenas e falta de equipamento, medicamentois e insumos.</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Falta de condicões de trabalho, inequidade na distribuicao de RH, sobrecarga das ESMI, falta de mentoria e AT.</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>1976</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>259.265</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>MISAU</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>122.400</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>24.480</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Relutância das ESMI em não encaminhar grávidas ARO para o clinico dentro da mesma US.</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_02.html</t>
         </is>
@@ -750,38 +846,68 @@
           <t>Calcular a idade gestacional (IG) para monitoria da gravidez, oferta de cuidados preventivos adequados à IG. Rastrear e Tratar as intercorrências da gravidez que afectam a mulher ou o feto, fazer seguimento e encaminhar atempadamente para o clinico ou US de referência para um desfecho favorável da gravidez. Aconselhamento em saúde.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enfermeiras de saude materno Infatil e clinicos da US capacitados em nutricao , aconselhamento e tratamento da desnutricao. Disponibilidade de Material, Equipamento e insumos de nutricao.  </t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formacao integrada de formadores nos pacotes de oferta de servicos na CPN,  que incluem nutricao, malaria, HIV, vacinacao, emergências. </t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Verticalizacao dos programas, sobrecarga das ESMI, multi-subordinacao das ESMI aos gestores de todos os programas oferecidos na CPN. Saturacao do Livro de registo da CPN, com muitas variáveis e não dá tempo a ESMI para obsevar adequadamente as utentes. Inúmeros livros na CPN (coorte, a mesma mulher está inscrita em vários livros e a ESMI deve procurar o livro anterior para seguimento do caso)</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>inexistência de um pacote único de formacao para as ESMI. Sobrecarga de trabalho sobretudo nas us periféricas dasgrandes cidades com um movimento elevado de utentes.</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Area coberta pelo Departamento de Nutricao</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_03.html</t>
         </is>
@@ -831,36 +957,66 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enfermeiras de saude materno Infatil , Disponibilidade de Sulfadoxina-Pirimetamina e Cotrimoxazol, redes mosquiteiras,  </t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Inducao de novas ESMI antes da sua alocacao à US alocada. Existência do medicamento. Monitoria e Avaliacao.</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>falta do medicamento SP e Corimoxazol para as HIV positivas</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Falta de fundos para a compra dos medicamentos. Advogacia junto às provedoras da importância da toma dO medicamentos e uso das RMTILD</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>1.700.000</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>1.530.000</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>90.0%</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_04.html</t>
         </is>
@@ -910,36 +1066,66 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Enfermeiras de saude materno Infantil capacitadas , Disponibilidade de Material e insumos Salferroso+ acido fólico, Cotrimoxazol, SP, redes mosquiteiras, Fitas de perimetro braquial, Balanca, altímetro. suplementos nutricionais. Hemoglobinómetros. Panelas, fogareiro e insumos para as demonstracoes culinárias para a mulher grávida e a família de acordo com sua idade</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inducao das Enfermeiras de SMI, equipamento, medicamentos e insumos específicos do programa de nutricao. </t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Conhecimentos sólidos de nutricao para aconselhamento e conduta. Falta de sessões culinárias nas US e nas comunidades.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Falta de insumos alimentícios e meios para confeccionamento. Rotura frequente de sal fderroso con ácido fólico.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>1976</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>595.000</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>162.435</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>78.0%</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_05.html</t>
         </is>
@@ -988,36 +1174,66 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Enfermeiras de saude materno Infatil capacitadas, Disponibilidade de esfigmomanómetros e AAS 100mg,  Nota técnica difundida.</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Formacao integrada da ESMI, mentoria e Apoio Técnico</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Falta de conhecimento e de AAS.</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Falta de divulgacao da circular e da AAS.</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>85.000</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>2.550</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_06.html</t>
         </is>
@@ -1066,36 +1282,66 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Enfermeiras de saude materno Infantil capacitadas a todos os níveis de atencao em saúde.  Disponibilidade de Material, Equipamento, medicamento para as patologias que levam ao parto pretermo, tocolíticos, Dexametaso e insumos ( testes de HIV, teste de Malaria, teste de urina para proteinúria, redes mosquiteiras, espéculos vaginais)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Formacao das Enfermeiras de SMI no pacote especifico, rastreio sistemático, insumos,  monitoria e avaliacao</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Falta de conhecimento</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Falta de formacoes e mentoria clinica</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>68.000</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2.040</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_07.html</t>
         </is>
@@ -1144,32 +1390,62 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Enfermeiras de saude materno Infatil , Disponibilidade de Material, Equipamento e insumos (Dexametasona, testes de HIV, Isoniazida, Salferroso+ acido falico, Cotrimoxazol, Tip Malaria, redes mosquiteiras, Fitas de perimetro braquial, Balaca, marqueza, estetoscopio de pinard, esfigmomanometro, termometro, )</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formacao de formadores em CPN, Formacao de Enfermeiras de SMI no pacote especifico de CPN, ARO, Nutricao,  Formacao em servico sobre o Alto Risco Obstetrico, Implementação de rastreios regulares,  enfermeiras de SMI no pacote especifico de nutricao </t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rotatividade do pessoal, baixa estigma,  </t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>A falta de infraestrutura adequada, equipamentos, medicamentos e materiais de consumo essenciais, Barreiras geográficas, socioeconômicas e culturais,  Condições de vulnerabilidade social, pobreza, violência ou ausência de suporte familiar podem afetar a adesão ao pré-natal e a continuidade do acompanhamento, Barreiras linguísticas ou de compreensão podem dificultar a transmissão de informações importantes às gestantes.</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>2.156.280</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>109.687</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>5.0%</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_08.html</t>
         </is>
@@ -1218,36 +1494,66 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Enfermeiras de saude materno Infatil actualizadas, Disponibilidade de Material, testes e insumos (Dexametasona, testes de HIV, Isoniazida, Salferroso+ acido falico, Cotrimoxazol, Tip Malaria, redes mosquiteiras, Fitas de perimetro braquial, Balanca,  estetoscopio de pinard, esfigmomanometro, termometro,  )</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Formacao e ctualizacao dos provedores, ARVs, medicamento para doencas oportunisticas, testagem do parceiro, Aconselhamento. PREp</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Falta de actualizacao e de medicamentos. Aconselhamento culturalmente sensiveis para adesao.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>sobrecarga de trabalho.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>391.000</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>387.000</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>99.0%</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_09.html</t>
         </is>
@@ -1296,40 +1602,70 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos em equipe capacitados e motivados, equipamento, medicamentos e insumos disponíveis. Sistma de referência e contra-referência funcionais e eficientes.</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garantir infraestrutura condignas e equipada., com equipamento e insumos. Treino em gestão de curta duracao das chefes das maternidades.ESMI suficientes e com actualizacao permanentel. Mentoria. Monitoria e Avaliacao. </t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Infraestruturas não coindignas ( mesma cada de banho para pessoal e doentes, falta de agua e energis nas maternidades, falta de equipamemto e medicamentos. Ambulância disponiveis e com combustivel, minimo 2 ambulancia para cada US de referencia. redefinir o funcionamento de ambulancias, todas as escalas de urgência devem ser presencial.</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Gestor com dificuldades de decisão, não proactivo. Falta de equipamentos, bens, produtos e insumos.</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>292.156</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>MISAU e parceiros</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>1.530.000</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>1.438.200</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>93,9%</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>Ha falta de Kits de parto e outro material medico coirurgico, marquezas, roupa de cama na quase totalidade das  Unidades Sanitarias, ventosas, partogramas, diário clinico e de enfermagen, requisicao de análises, bloco de receitas, instrumentos de registo.</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_10.html</t>
         </is>
@@ -1376,42 +1712,52 @@
           <t>Garantir a saúde da mulher e seu futuro reprodutivo</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1.615.000</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1.324.300</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>82.0%</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Há escassez severa de tudo nas US</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_11.html</t>
         </is>
@@ -1461,40 +1807,70 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>ESMI e clinicos actaulizados. Visita do clinico diária e permanente. Equipamento, medicamentoa e diários clinico e de enfermagem. Instrumentos de registo</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Monitoria do desempenho dos profissionais de SMI</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Ausencia e comprometimento dos gestores</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Falta de comprometimento individual. Atitude.</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S/ Informação </t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>1.700.000</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>1.402.500</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>82.5%</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Tem défice de espéculos em algumas unidades Sanitárias e algumas sem autoclave para a esterilização do material. Dependendo de uma outra unidade sanitária mais proxima para esterilizar.  Por falta do material as ESMI optam por usar condutas proibidas que é o toque vaginal. </t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_12.html</t>
         </is>
@@ -1543,41 +1919,71 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Medicamento aborivo Miso-Mife, seringas e canulas de aspiracao, kit de ginecologia. Treino das provedoras.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Equipar os servicos e treinar as ESMI e clinicos</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>ESMI não treinadas e capacitadas</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>falta de fundos para capacitacao _ CONEm</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Parceiros
 </t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>170.000</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>20.400</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>12.0%</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Tem havido falta do Miso-Mife, dificultando a provisao dos servicos</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_13.html</t>
         </is>
@@ -1626,37 +2032,67 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>ESMI capacitada. Ecógrafo, Esfigmomanómetro, termómetro, antibioticos, sal ferroso</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>ESMI capacitada. Visita diária do clinico na maternidade</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>falta de insumos e clinico na maternidade</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Parceiros
 </t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>170.000</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>62.900</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>37.0%</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_14.html</t>
         </is>
@@ -1705,36 +2141,66 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ESMI capacitada. Ecógrafo, Esfigmomanómetro, termómetro, antibioticos, sal ferroso</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>ESMI capacitada. Visita diária do clinico na maternidade</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>falta de insumos e clinico na maternidade</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Gestão</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>S/I</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>MISAU E Parceiros</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>8.159.149</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>244.775</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>3.0%</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>S/I</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_15.html</t>
         </is>
@@ -1787,42 +2253,73 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado para a oferta dos Cuidados Essenciais do Recém-Nascido (CERN)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Capacitação das Enfermeiras de Saúde Materno-Infantil (ESMI) em CERN/AIDI NN
+Monitoria das actividades (mentoria)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baixo cumprimento das normas (CERN)
+Escassez de ESMI
+Disponibilidade irregular de insumos </t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Alta rotatividade do pessoal capacitado no pacote do CERN
+Falta de Motivação do pessoal
+Dificuldades logísticas</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Banco Mundial
  UNICEF
  USAID</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>1.401.849</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>0.63 USD</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>O número de crianças que recebeu clorexidina Gel não vêm refletido no SIS-MA</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_16.html</t>
         </is>
@@ -1874,36 +2371,68 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado para a oferta dos Cuidados Essenciais do Recém-Nascido (CERN)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Capacitação das Enfermeiras de Saúde Materno-Infantil (ESMI) em CERN/AIDI NN
+Monitoria das actividades (mentoria)</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Baixo cumprimento das normas (CERN) 
+Escassez de ESMI
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado no pacote do CERN
+Falta de Motivação do pessoal
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>MISAU</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1.401.849</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>O número de crianças que recebeu Tetraciclina Pomada Oftálmica não vêm refletido no SIS-MA</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_17.html</t>
         </is>
@@ -1957,36 +2486,68 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado para a oferta dos Cuidados Essenciais do Recém-Nascido (CERN)</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Capacitação das Enfermeiras de Saúde Materno-Infantil (ESMI) em CERN/AIDI NN
+Monitoria das actividades (mentoria)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Baixo cumprimento das normas (CERN) 
+Escassez de ESMI
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado no pacote do CERN
+Falta de Motivação do pessoal
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>MISAU</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>1.401.849</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>O número de crianças que recebeu Vitamina K não vêm refletido no SIS-MA</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="V19" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_18.html</t>
         </is>
@@ -2038,32 +2599,64 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado para a oferta dos Cuidados Essenciais do Recém-Nascido (CERN)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Capacitação das Enfermeiras de Saúde Materno-Infantil (ESMI) em CERN/AIDI NN
+Monitoria das actividades (mentoria)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Baixo cumprimento das normas (CERN) 
+Escassez de ESMI
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Alta rotatividade do pessoal capacitado no pacote do CERN
+Falta de Motivação do pessoal
+Mentoria irregular das actividades</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>2009 (contacto pele-a-pele)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>UNICEF</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1342273 (Partos eutócicos)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1.333.729</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1342273 (Partos eutócicos)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1.333.729</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_19.html</t>
         </is>
@@ -2116,20 +2709,52 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal treinado no Pacote de PTV (Prevenção da Transmissão Vertical)</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Capacitação das Enfermeiras de Saúde Materno-Infantil (ESMI) no Pacote de PTV
+Monitoria das actividades (mentoria)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas (PTV)
+Disponibilidade irregular dos ARVs
+Identificação tardia de mulheres grávidas vivendo com HIV
+Escassez de ESMI</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Alta rotatividade do pessoal capacitado no pacote de PTV
+Falta de Motivação do pessoal
+Mentoria irregular das actividades</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>Inicio do PTV 2002</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>Quantificação dos Arvs feitos ao nível do Programa Nacional de Controle de ITS/HIV-SIDA</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_20.html</t>
         </is>
@@ -2182,33 +2807,70 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Pessoal treinado em Reanimação Neonatal
+Disponibilidade de materiais e equipamentos</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Elaboração dos materiais de formação (AIDI/NN)
+Elaboração e reprodução de Material de IEC
+Treinamento do pessoal em reanimação neonatal
+Alocação dos cantinhos de reanimação do recém-nascido
+Aquisição de material e medicamentos essenciais</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento dos protocolos de reanimação 
+Escassez de ESMI
+Disponibilidade irregular de insumos (medicamentos e materiais)
+Disponibilidade limitada  de equipamentos essenciais</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Alta rotatividade do pessoal capacitado em reanimação neonatal
+Falta de Motivação do pessoal
+Mentoria irregular das actividades
+Dificuldades logísticas</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>2010 (normas de Reanimação Neonatal)</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>UNICEF
  CHAI</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>12.685</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>12.427</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>98.0%</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_21.html</t>
         </is>
@@ -2260,29 +2922,70 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pessoal treinado em Método Mãe Canguru
+Identificação de um canto para a implementação 
+Material e equipamento: camas articuladas; fonte de calor radiante (UCR); termómetros; copinhos graduados; sondas de alimentação; seringas, catéteres; medicamentos
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Elaboração dos materiais de formação (Método Mãe Canguru)
+Elaboração e reprodução de Material de IEC
+Treinamento do pessoal em reanimação neonatal
+Alocação dos cantinhos de reanimação do recém-nascido
+Aquisição de material e medicamentos essenciais</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas 
+Falta de espaço para a implementação do Método Mãe- Canguru (MMC)
+Escassez de ESMI
+Disponibilidade irregular de insumos
+Disponibilidade limitada  de equipamentos essenciais
+Falta de financiamento para a expansão e revitalizaçãodas unidades Canguru</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado em Método Mãe Canguru (MMC)
+Falta de Motivação do pessoal
+Mentoria irregular das actividades
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>1984 (MMC)</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>UNICEF
 OMS</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>17.014</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_22.html</t>
         </is>
@@ -2334,29 +3037,70 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pessoal treinado em Método Mãe Canguru
+Identificação de um canto para a implementação 
+Material e equipamento: camas articuladas; fonte de calor radiante (UCR); termómetros; copinhos graduados; sondas de alimentação; seringas, catéteres; medicamentos
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Elaboração dos materiais de formação (Método Mãe Canguru)
+Elaboração e reprodução de Material de IEC
+Treinamento do pessoal em reanimação neonatal
+Alocação dos cantinhos de reanimação do recém-nascido
+Aquisição de material e medicamentos essenciais</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas 
+Falta de espaço para a implementação do Método Mãe- Canguru (MMC)
+Escassez de ESMI
+Disponibilidade irregular de insumos
+Disponibilidade limitada  de equipamentos essenciais
+Falta de financiamento para a expansão e revitalizaçãodas unidades Canguru</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado em Método Mãe Canguru (MMC)
+Falta de Motivação do pessoal
+Mentoria irregular das actividades
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>1984 (MMC)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>UNICEF
 OMS</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>33.775</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_23.html</t>
         </is>
@@ -2416,22 +3160,49 @@
           <t>Reduzir a mortalidade neonatal</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado
+Material: Termómetro, Cronómetros, balanças pediátricas, fita de perímetro craniano e altímetro</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>1.401.849</t>
+          <t>Formações contínuas</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr"/>
+          <t xml:space="preserve">Baixo cumprimento das normas </t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Sobrecarga de trabalho</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>1.401.849</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_24.html</t>
         </is>
@@ -2482,10 +3253,55 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Pessoal treinado em AIDINN
+Material de formação e IEC
+Insumos (medicamentos e material)
+Equipamentos</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Elaboração dos materiais de formação
+Elaboração e reprodução de Material  IEC
+Treinamento do pessoal 
+Aquisição de material e medicamentos essenciais
+Revitalizar os berçarios à nível rural e distrital</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas
+Escassez de ESMI
+Disponibilidade irregular de insumos (medicamentos e materiais)
+Disponibilidade limitada  de equipamentos essenciais
+Falta de financiamento para a revitalização e apetrechamento das unidades neonatais
+Falta de infraestruturas adequadas para a referência dos Recém-nascidos graves</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado 
+Falta de Motivação do pessoal
+Mentoria irregular das actividades
+Dependência de financiamento externo
+Cobertura geográfica desigual; 
+Deficiência em transporte neonatal;
+Infraestrutura hospitalar insuficiente 
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>UNICEF
  CHAI
@@ -2493,20 +3309,20 @@
  SAVE THE CHILDREN</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_25.html</t>
         </is>
@@ -2558,10 +3374,51 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado
+Espaço Físico: Gabinete, alpendre;
+Material: balança de prato; balança pêndulo; altímetro; fitas para avaliação do perímetro braquial; tabelas de referência de meninas e rapazes e Ferramenta de rastreio de MDAT-IDEC;  livros de registo da consulta da criança sadia; livros de resumo diário e mensal da unidade sanitária e cartões de saúde; algorítmos de HIV e Tuberculose.
+Insumos: Testes de HIV; suplementos (Vitamina A) e desparasitantes (albendazol e mebendazol); vacinas</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaboração dos materiais de formação: MDAT-IDEC e DPI.
+Elaboração e reprodução de Material  IEC
+Treinamento do pessoal 
+Aquisição de material e suplementos (Vitamina A) e desparasitantes (albendazol e mebendazol); vacinas
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas
+Escassez de ESMI
+Falta de financiamento para a construção de gabinetes ou alpendres de CCS
+Falta de infraestruturas adequadas para a implementação das actividades</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado 
+Falta de Motivação do pessoal
+Sobrecarga de trabalho
+Mentoria irregular das actividades
+Dependência de financiamento externo
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>PATH
  OMS
@@ -2569,24 +3426,24 @@
  Alcançar/FHI 360</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>5262815 (INE: 0-59 meses)</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>1739751 (0-59 MESES)</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="S27" s="3" t="inlineStr">
         <is>
           <t>33.0%</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="inlineStr">
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_26.html</t>
         </is>
@@ -2636,8 +3493,50 @@
           <t>Reduzir a mortalidade infantil</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Pessoal qualificado
+Espaço Físico: gabinete
+Material: balança de prato; balança pêndulo; altímetro; fitas para avaliação do perímetro braquial; tabelas de referência de meninas e rapazes e Ferramenta de rastreio de MDAT-IDEC;  livros de registo da consulta da criança em risco; livros de resumo diário e mensal da unidade sanitária;  cartões de saúde e ficha de seguimento da criança; algorítmos (HIV, Tuberculose, etc) 
+Insumos: Testes rápidos de HIV; DBS para PCR-DNA; Sífilis e Mantoux; suplementos (Vitamina A);  desparasitantes (albendazol e mebendazol); ARVs profiláticos;  profilaxia para Tuberculose e ATPU.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaboração dos materiais de formação: DPI (Desenvolvimento da Primeira Infância)
+Elaboração e reprodução de Material  IEC
+Treinamento do pessoal 
+Aquisição de material e insumos
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas
+Escassez de ESMI
+Falta de financiamento para a construção de gabinetes de CCR
+Falta de infraestruturas adequadas para a implementação das actividades
+Implementação das demonstrações culinárias de forma irregular</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado 
+Falta de Motivação do pessoal
+Sobrecarga de trabalho
+Mentoria irregular das actividades
+Dependência de financiamento externo
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>PATH
  OMS
@@ -2645,20 +3544,20 @@
  Alcançar/FHI 360</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>16.060.835</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_27.html</t>
         </is>
@@ -2709,10 +3608,52 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Pessoal treinado em AIDI
+Material de formação e IEC
+Insumos (medicamentos e material)
+Equipamentos</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Elaboração dos materiais de formação
+Elaboração e reprodução de Material  IEC
+Treinamento do pessoal 
+Aquisição de material e medicamentos essenciais ( SRO+ZINCP; Amoxicilina; Ciprofloxacina; paracetamol; antimaláricos, entre outros.
+Revitalizar os cantinhos de reidratação oral, compostos por copos plásticos, bacia plástica, tabuleiros e jarros coloridos</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Baixo cumprimento das normas
+Escassez de ESMI e clínicos dedicados ao AIDI 
+Disponibilidade irregular de medicamentos (SRO+Zinco); Amoxicilina dispersível de 250mg; xarope de sal ferroso
+Disponibilidade limitada de  materiais e  equipamentos essenciais (cronómetros, termómetros, oxímetros, cantinhos de reidratação oral)
+Falta de financiamento para aquisição e compra dos kits de SRO+Zinco
+Falta de infraestruturas adequadas para atendimento (gabinentes de CCD)</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alta rotatividade do pessoal capacitado 
+Falta de Motivação do pessoal
+Mentoria irregular das actividades
+Dependência de financiamento externo
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">UNICEF
  CHAI
@@ -2721,20 +3662,20 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>Atendidos na CCD</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
-      <c r="P29" s="3" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_28.html</t>
         </is>
@@ -2781,28 +3722,58 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>Profissionais de saúde capacitados, Aquisição do contraceptivo, sistemas logístico, materiais de aconselhamento</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1-Quantificação e aquisição; 2-Distribuição as US; 3-Capacitação dos prvedores;4-Oferta dos métodos nas consultas; 4-Monitoria do uso</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Ruptura de stock;  Baixa adesão das utentes; Falta de aconselhamento adequado</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Problemas logísticos, barreiras socio-culturais; falta de informação sobre o método, dependêcia de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>2.195.424</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>MIF's= 8159149</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>Casal Ano Protegido= 361599</t>
         </is>
       </c>
-      <c r="M30" s="2" t="e">
+      <c r="S30" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_29.html</t>
         </is>
@@ -2849,21 +3820,47 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="e">
-        <v>#DIV/0!</v>
+          <t>Profissionais de saúde capacitados, Aquisição do contraceptivo, sistemas logístico, materiais de aconselhamento</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>1-Quantificação e aquisição; 2-Distribuição as US; 3-Capacitação dos prvedores;4-Oferta dos métodos nas consultas; 4-Monitoria do uso</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Ruptura de stock;  Uso icorrecto do método</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Problemas logísticos, barreiras socio-culturais; falta de informação sobre o método; dependência de financiamento externo</t>
+        </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="inlineStr">
         <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_30.html</t>
         </is>
       </c>
@@ -2911,26 +3908,56 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Profissionais de saúde capacitados, Aquisição do contraceptivo, sistemas logístico, materiais de aconselhamento</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1-Quantificação e aquisição; 2-Distribuição as US; 3-Capacitação dos prvedores;4-Oferta dos métodos nas consultas; 4-Monitoria do uso</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ruptura de stock; </t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Problemas logísticos; dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>651.600</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>Casal Ano Protegido = 1234207</t>
         </is>
       </c>
-      <c r="M32" s="2" t="e">
+      <c r="S32" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_31.html</t>
         </is>
@@ -2977,20 +4004,50 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>Profissionais de saúde capacitados, Aquisição do contraceptivo, sistemas logístico, materiais de aconselhamento</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>1-Quantificação e aquisição; 2-Distribuição as US; 3-Capacitação dos prvedores;4-Oferta dos métodos nas consultas; 4-Monitoria do uso</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Ruptura de stock</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Problemas logísticos,  dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>895.200</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="e">
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
-      <c r="P33" s="3" t="inlineStr">
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_32.html</t>
         </is>
@@ -3037,20 +4094,50 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>Implante-Levoplant, kits de inserção e remoção, profissionais capacitados, material clínico, lidocaína</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Aquisição, Formação em inserção e remoção, disponibilização do Levoplant nas US</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Insuficiência de profissionais treinados, complicações na inserção e remoção, ruptura de stock</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Falta de práticas durante a  formação, problemas logísticos, dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>78.000</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="e">
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_33.html</t>
         </is>
@@ -3097,28 +4184,58 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>Implante-Jadelle, kits de inserção/remoção, profissionais capacitados, material clínico, lidocaína</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição, Formação em inserção e remoção, disponibilização do Jadelle nas US</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Insuficiência de profissionais treinados, complicações na inserção e remoção, ruptura de stock</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Falta de práticas durante a  formação, problemas logísticos, dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>35.600</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>8.159.149</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Casal Ano Protegido= 2650599</t>
         </is>
       </c>
-      <c r="M35" s="3" t="e">
+      <c r="S35" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr"/>
-      <c r="P35" s="3" t="inlineStr">
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_34.html</t>
         </is>
@@ -3165,24 +4282,54 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>Implante-Implanon, kits de inserção/remoção, profissionais capacitados, lidocaína</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Aquisição, Formação em inserção e remoção, disponibilização do Implanon nas US</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Insuficiência de profissionais treinados, complicações na inserção e remoção, ruptura de stock</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Falta de práticas durante a  formação, problemas logísticos, dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>43.152</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>USAID/UNFPA</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>Casal Ano Protegido= 335980</t>
         </is>
       </c>
-      <c r="M36" s="2" t="e">
+      <c r="S36" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_35.html</t>
         </is>
@@ -3229,25 +4376,51 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
+          <t>DIU, kits de inserção, profissionais treinados, material clínico</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição do produto, Formação em inserção e remoção, disponibilização do DIU nas US</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Casal Ano Protegido= 974344</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="e">
-        <v>#VALUE!</v>
+          <t>Baixa procura do método,  falta de técnios capacitados</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Mitos e percepções negativas, falta de aconselhamento adequado, dependência de financiamento externo</t>
+        </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>Casal Ano Protegido= 974344</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr"/>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_36.html</t>
         </is>
       </c>
@@ -3295,22 +4468,48 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>Nacional (incluindo US e distribuição comunitária)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Aquisição de preservativos masculinos, sistema logistico, campanhas de sensibilização</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Aquisição, Distribuição, Sensibilização  comunitária</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Baixo uso consistente</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Barreiras culturais, falta de sensibilização, dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_37.html</t>
         </is>
@@ -3359,20 +4558,46 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
+          <t>Nacional (incluindo US e distribuição comunitária)</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição de preservativos femininos, sistema logistico, campanhas de sensibilização</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição, Distribuição, Sensibilização  comunitária</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Baixo uso consistente</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Barreiras culturais, falta de sensibilização, dependência de financiamento externo</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>2012?</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA/Fundo Global</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA/Fundo Global</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_38.html</t>
         </is>
@@ -3419,21 +4644,47 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>UNFPAUNFPA/Fundo Global</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="e">
-        <v>#DIV/0!</v>
+          <t>Aquisição de contraceptivo, profissionais capacitados, oferta nas US</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Aquisição e distribuição, capacitação de profissionais e oferta nas US</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Uso inadequado, falta de informação</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Desconhecimento da população, Barreiras socio-culturais, dependência do financiamento externo</t>
+        </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
+          <t>UNFPAUNFPA/Fundo Global</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_39.html</t>
         </is>
       </c>
@@ -3479,14 +4730,40 @@
           <t>Reduzir a Mortalidade Materna e reduzir gravidez indesejada</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição de contraceptivos, profissionais capacitados, oferta nas US</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição e distribuição, capacitação de profissionais e oferta nas US</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Estigma e barreiras socioculturas que limitam o acesso dos adolescentes e jovens aos serviços, falta de SAAJ específicos nas Us, ruptura de stock de métodos contraceptivos</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Normas culturais e sociais que desencorajam adolescentes e jovens a procurar serviços de saúde sexual e reprodutiva,  falta de sensibilização das comunidades e famílias, recursos financeiros e humanos limitados, problemas na cadeia logística de abastecimento de insumos, dependência do financiamento externo</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="3" t="inlineStr">
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr"/>
+      <c r="V41" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_40.html</t>
         </is>
@@ -3535,22 +4812,48 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Provedores de saúde capacitados em PF, métodos contraceptivos disponíveis nas portas de integração, material de aconselhamento e normas clínicas, sistema logistico funcional para abastecimento de contraceptivos, instrumentos de registo</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Orientação e capacitação dos profissionais de saúde sobre PF integrado, disponibilização de métodos contraceptivos nas diferentes consultas, aconselhamento em PF em todos os pontos de contacto com utentes, supervisão e monitoria da implementação</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Sobrecarga de trabalho dos profissionais de saúde, falta de integração efectiva entre serviços, ruptura de stock de contraceptivos</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos insuficientes, falta de formação específica sobre integração de serviços, problemas na cadeia logística de medicamentos, dependência do financiamento externo</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_41.html</t>
         </is>
@@ -3599,22 +4902,48 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
+          <t>Nacional a nível da comunidade através dos APSs (excepto Maputo Cidade devido a característica urbana)</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APSs capacitados em PF, métodos contraceptivos (orais e sayana além de preservativos) disponiveis </t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Capacitação dos APSs em aconselhmento e provisão de PF, disponibilização de contrceptivos aos APSs, sensibilização comunitária, referência de utentes para Us quando necessário, monitoria e supervisão das actividades</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Limitações na capacitação dos APSs, resistência sociocultural ao uso de contraceptivos, falta de abastecimento regular de métodos</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>barreiras culturais e religiosas, problemas logísticos de distribuição, dependência do financiamento externo</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_42.html</t>
         </is>
@@ -3663,26 +4992,52 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Profissionais de saúde capacitados em PF pós-parto, métodos contraceptivos disponíveis, materiais de aconselhamento, normas e protocolos clínicos</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Aconselhamento em PF durante a CPN e pós-parto imediato, disponibilização de métodos contrcaeptivos antes da alta da maternidade</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Falta de aconselhamento adequado na CPN, Falta de métodos contraceptivos nas maternidades, baixa aceitação por parte das utentes</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Mitos e percepções culturais, negativas, falhas no abastecimento, dependência do financiamento externo</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>DIU pós-parto =92540</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>DIU pós-parto =92540</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_43.html</t>
         </is>
@@ -3731,22 +5086,48 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nacional </t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Profissionais de saúde capacitados, disponibilidade de métodos contraceptivos incluindo contracepção de emergência, normas e protocolos clínicos, materiais de aconselhamento</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Capacitação de profissionais de saúde na oferta de PF na urgência de gin., disponibilização de contracepção de emergência, aconselhamento as utentes atendidas</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>falta de para aconselhamento para o PF, falta de disponibilidade de métodos</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Sobrecarga dos serviços, problemas logisticos, dependência do financiamento externo</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_44.html</t>
         </is>
@@ -3795,22 +5176,48 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t>Das 11 províncias esta em falta a província de Gaza (Previsão Março 2026) para alcance a nível nacional</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Disponibilidade de DMPA-SC (Sayana Press),  Material para formação para auto-injecção, provedores capacitados, material IEC, sistema de monitoria e acompanhamento</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Formação de profissionais de saúde, Capacitação das utentes em auto-injecção, distribuição do método para o uso domiciliar, supervisão e monitoria do uso correcto</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Uso incorrecto da auto-injecção, falta de aceitação comunitária, ruptura de stock</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Fraca literacia em saúde, Falta de formação adequada, problemas logísticos, dependência do financiamento externo</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>USAID/UNFPA</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>USAID/UNFPA</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_45.html</t>
         </is>
@@ -3859,40 +5266,70 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
+          <t>Unidades sanitarias e comunidades</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos para implementacao da actividade, recursos financeiro</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>1. Selecção: Definir a lista de medicamentos/suplementos essenciais.                                            2. Programação: Estimar as quantidades necessárias baseada no consumo histórico ou grupos-alvo.                                                         3. Fazer advocacia aos parceiros para aquisição: Compra de suplementos/medicamentos planificados e disponibilizar a CMAM                                   4. Armazenamento e Acondicionamento: monitoria de stocks e controle rigoroso do prazo de validade e fazer a analise das requisicoes.                                                 5. Distribuição e Transporte: Acompanhar a distribuicao ate aos DPM e AI.</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>2.807.870</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>Banco Mundial, UNICEF e WFP</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>5.262.815</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>192.567</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="S47" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N47" s="3" t="inlineStr">
+      <c r="T47" s="3" t="inlineStr">
         <is>
           <t>175.18</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="U47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Exercicio de planificação para responder a toda a demanda do programa quer em ensumos, materiais como a monitoria e desempenho </t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr">
+      <c r="V47" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_46.html</t>
         </is>
@@ -3941,36 +5378,66 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
+          <t>Unidades sanitarias e comunidades</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>1- Fazer o plano de necessidades;                          2- Advocar para finaciamento, aquisicao e distribuicao</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Falta de finaciamento</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_47.html</t>
         </is>
@@ -4019,36 +5486,66 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1- Ter dados do SISMA a partir do dia 16 de cada trimestre;                                     2- Fazer analise e garantir a divulgacao  </t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fraca colaboracao a todos os niveis </t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>29.857</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
         <is>
           <t>HKI</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>Profissionais de Saude</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3 provincias </t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="S49" s="3" t="inlineStr">
         <is>
           <t>12 Distritos</t>
         </is>
       </c>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="T49" s="3" t="inlineStr">
         <is>
           <t>Nampula-10048 USD                      Sofala- 9762 USD                    Zambezia- 10048 USD</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr"/>
-      <c r="P49" s="3" t="inlineStr">
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_48.html</t>
         </is>
@@ -4097,36 +5594,62 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>Comunidades e US</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Coordenação entre unidades e comunidades, Materiais de Antropometrico, fitas de perimetro Branqueal, Craneano</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Resistência para mudança de comportamento nos serviços de saúde</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Lacunas no conhecimento sobre saúde algumas materias</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>14.791</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>5.262.815</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>8.962.806</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="T50" s="2" t="inlineStr">
         <is>
           <t>$ 25,95</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr">
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_49.html</t>
         </is>
@@ -4175,36 +5698,66 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Material antropometrico, fitas de PB,  Suplenetos necessario</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Supervisão e avaliação contínua do programa</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades na implementação devido a falta de insumos em algumas vezes</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Ropturas frequentes dos insumos</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>54.853</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>1662221  de MG</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>1.783.098</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="S51" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N51" s="3" t="inlineStr">
+      <c r="T51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 0,033</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr"/>
-      <c r="P51" s="3" t="inlineStr">
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_50.html</t>
         </is>
@@ -4253,40 +5806,70 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Material antropometrico, fitas de PB,  Suplenetos necessario</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Supervisão e avaliação contínua do programa</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades na implementação devido a falta de insumos em algumas vezes</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Ropturas frequentes dos insumos</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>320.250</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>12.568</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>12.568</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="T52" s="2" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="U52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Tratamento nutricional  a crianças com Desnutrição aguda  </t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_51.html</t>
         </is>
@@ -4335,36 +5918,66 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Material antropometrico, fitas de PB,  Suplenetos necessario</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Supervisão e avaliação contínua do programa</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades na implementação devido a falta de insumos em algumas vezes</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Ropturas frequentes dos insumos</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>742.413</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>106.966</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>133.439</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="S53" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="T53" s="3" t="inlineStr">
         <is>
           <t>$ 0,33</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr"/>
-      <c r="P53" s="3" t="inlineStr">
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_52.html</t>
         </is>
@@ -4413,36 +6026,66 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Material antropometrico, fitas de PB,  Suplenetos necessario</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Supervisão e avaliação contínua do programa</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades na implementação devido a falta de insumos em algumas vezes</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Ropturas frequentes dos insumos</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>25.949</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>85.573</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>78.636</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="S54" s="2" t="inlineStr">
         <is>
           <t>91.9%</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="T54" s="2" t="inlineStr">
         <is>
           <t>$ 0,33</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_53.html</t>
         </is>
@@ -4491,40 +6134,70 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Profissionais de saúde qualificados</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Sal ferroso disponivel para suplementacao</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>Inicio  em 2002,</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>133.500</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>3.158.220</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>2.744.268</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="S55" s="3" t="inlineStr">
         <is>
           <t>86.9%</t>
         </is>
       </c>
-      <c r="N55" s="3" t="inlineStr">
+      <c r="T55" s="3" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="U55" s="3" t="inlineStr">
         <is>
           <t>Suplementação com duas doses anuais de vitamina A as crianças dos 6-59 meses</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr">
+      <c r="V55" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_54.html</t>
         </is>
@@ -4573,36 +6246,66 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>Unidades sanitarias</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e profissionais de saude</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Suplimentaçao com ferro e acido folico</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>4.364.555</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>1.979.052</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="S56" s="2" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="T56" s="2" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_55.html</t>
         </is>
@@ -4649,38 +6352,56 @@
           <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr"/>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>136.096.290</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>UNICEF</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>4.124.130</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>3.803.415</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="S57" s="3" t="inlineStr">
         <is>
           <t>92.2%</t>
         </is>
       </c>
-      <c r="N57" s="3" t="inlineStr">
+      <c r="T57" s="3" t="inlineStr">
         <is>
           <t>$ 0,033</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr"/>
-      <c r="P57" s="3" t="inlineStr">
+      <c r="U57" s="3" t="inlineStr"/>
+      <c r="V57" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_56.html</t>
         </is>
@@ -4723,30 +6444,52 @@
           <t>contribuindo para a melhoria do estado nutricional, crescimento, desenvolvimento e saúde geral, especialmente em crianças e outros grupos vulneráveis.</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e profissionais de saude</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Desparasitaçao  gravida</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
         <is>
           <t>1.662.221</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>1.783.090</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="S58" s="2" t="inlineStr">
         <is>
           <t>107.3%</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr">
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_57.html</t>
         </is>
@@ -4793,34 +6536,60 @@
           <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e profissionais de saude</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Suplimentacao com MNP</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>23.463.499</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">BANCO Mundal </t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>2.224.037</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="R59" s="3" t="inlineStr">
         <is>
           <t>1.688.331</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="S59" s="3" t="inlineStr">
         <is>
           <t>75.9%</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr"/>
-      <c r="P59" s="3" t="inlineStr">
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_58.html</t>
         </is>
@@ -4863,18 +6632,36 @@
           <t xml:space="preserve">Prevenção da deficiência de Micronutrientes </t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e profissionais de saude</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_59.html</t>
         </is>
@@ -4921,34 +6708,60 @@
           <t>Prevenção da deficiencia de vitaminaA - Segueria  Notura  - redução dos actuais 64%</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recursos financeiros </t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Suplimentaçao com Vitamina A</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>1.721.692</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>Banco Mundial, UNICEF</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>1.138.685</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>1.599.356</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="S61" s="3" t="inlineStr">
         <is>
           <t>140.5%</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
-      <c r="P61" s="3" t="inlineStr">
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr"/>
+      <c r="V61" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_60.html</t>
         </is>
@@ -4995,34 +6808,60 @@
           <t>Prevenção da deficiência de micronutrientes e assim redução da DC</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recursos financeiros </t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Suplimentaçao com Vitamina A</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>5.716.044</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>Banco Mundial, UNICEF</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="Q62" s="2" t="inlineStr">
         <is>
           <t>4.124.130</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>2.624.187</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="S62" s="2" t="inlineStr">
         <is>
           <t>63.6%</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr">
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_61.html</t>
         </is>
@@ -5069,22 +6908,48 @@
           <t>Redução da Desnutrição crónica, desnutrição aguda   e deficiência de micronutrientes  e melhoria das praticas de nutricao na comunidade  a partir de uma intervenção de elevado impacto com foco nos 1000 dias</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e profissionais de saude</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Aconselhamento em aleitamento materno exclusivo, alimentação complementar adequada e Higiene e saneamento do Meio,  Monitoria do crescimento p/I; suplementação com Vitamina A  e Micronutriente em pó dos 6-23 meses e Desparasitação. Para o alcance de crianças com o PIN completo e prevenção de todas as formas de desnutrição</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Falta de acesso ao sIGLUS para a minitoria de stocks e prazos de validade</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Fraca quantificacao dos suplementos/medicamentos</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>2.175.143</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
         <is>
           <t>Banco Mundial, UNICEF</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
-      <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr"/>
-      <c r="P63" s="3" t="inlineStr">
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr"/>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_62.html</t>
         </is>
@@ -5133,32 +6998,67 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
+          <t>Comunidades e US</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Utensilios domesticos, alimentos e recursos humanos</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>1. Conheça seu público/audiência. Quanta experiência ou conhecimento eles têm? O que você quer que eles aprendam durante a demonstração?
+2. Tenha uma mensagem nutricional clara e simples.
+3. Seja organizado e bem preparado.
+4. Use receitas apropriadas.
+5. Certifique-se de que a área de demonstração seja colorida e atraente e capte a atenção do público.
+6. Incorpore informações nutricionais em toda a demonstração. 
+7. Incentive os participantes a provarem a comida assim que a receita estiver pronta.
+8. Siga sempre as diretrizes de segurança de alimentos.
+9. Forneça aos participantes receitas para levarem para casa, como panfletos ou brochuras adicionais que ajudarão a reforçar a mensagem nutricional.
+10. Use avaliações para ajudar a direcionar demonstrações futuras</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Falta de alimentos, agua e utensilios convencionais e locais. Existencia de praticas e tabus culturais relaionados a alimentacao da crianca e da mulher gravida/lactante</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>inseguranaca alimentar (limitada disponiblidade e acesso a alimentos nas machambas e mercados)</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>OE</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>106.966</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>42.184</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>39.4%</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>106.966</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>42.184</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>39.4%</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_63.html</t>
         </is>
@@ -5207,32 +7107,64 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
+          <t>comunidades e US</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Material de informacao educacao e comunicacao (folhetos, cartazes, spots, albuns seriados, Emo-Demos e outros materias de visibilidade, livros de bolso)</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>1. Conheça seu público/audiência. Quanta experiência ou conhecimento eles têm? O que você quer que eles aprendam durante a palestra?
+2. Tenha uma mensagem nutricional clara e simples.
+3. Seja organizado e bem preparado.
+4. Use material de IEC apropriado.
+5. Certifique-se de que a área da palestra atraente e capte a atenção do público.
+6. Incorpore informações chave nutricionais em toda a palestra. 
+7. Use avaliações para ajudar a direcionar palestras futuras</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Falta de material de IEC actualizado para diferentes tematicas</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Falta de recursos para actualizacao, reproducao e disseminacao</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>OE</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>106.966</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>151.107</t>
-        </is>
-      </c>
-      <c r="M65" s="3" t="inlineStr">
-        <is>
-          <t>141.3%</t>
-        </is>
-      </c>
-      <c r="N65" s="3" t="inlineStr"/>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>106.966</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>151.107</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>141.3%</t>
+        </is>
+      </c>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr"/>
+      <c r="V65" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_64.html</t>
         </is>
@@ -5281,16 +7213,46 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Recursos Humanos e financeiros, fichas de monitoria e brochura do codigo de comercializacao dos substitutos do leite materno</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treinamento dos profissionais de saude, senssibilizacao e  inspeccoes </t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Falta de recursos financeiros pararealizacao das monitorias e inspeccoes.                                                                                          Alta rotatividade de profissionais de saúde.</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Falta de transporte e recursos para a equipe de monitoramento e fiscalizacao</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
-      <c r="P66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>200.000</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_65.html</t>
         </is>
@@ -5339,16 +7301,46 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Recursos Humanos e financeiros, fichas de monitoria e brochura do codigo de comercializacao dos substitutos do leite materno</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treinamento dos profissionais de saude, senssibilizacao e  inspeccoes </t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Falta de recursos financeiros pararealizacao das monitorias e inspeccoes.                                                                                          Alta rotatividade de profissionais de saúde.</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Falta de transporte e recursos para a equipe de monitoramento e fiscalizacao</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr"/>
-      <c r="P67" s="3" t="inlineStr">
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>200.000</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr"/>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr"/>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr"/>
+      <c r="V67" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_66.html</t>
         </is>
@@ -5395,18 +7387,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Todas as Provincias - Unidades Sanitaria</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Viaturas e combustível; equipamentos de cadeia de frio; geleiras e acumuladores; sistema SELV/logística; técnicos de logística; fundos operacionais</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
+          <t>Actualizar plano logístico; quantificar necessidades; planificar rotas; distribuir vacinas às províncias e distritos; monitorar stocks; supervisão logística</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Ruptura de stock; falhas na cadeia de frio; atrasos na distribuição</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Questoes financeiras afectam a aquisição e distribuição de vacinas</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>552.536</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr">
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_67.html</t>
         </is>
@@ -5453,18 +7475,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Todas as Provincias - Unidades Sanitaria</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Equipas de vacinação; transporte (viaturas/motas); vacinas e consumíveis; geleiras portáteis; ajudas de custo; microplanos</t>
+        </is>
+      </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
+          <t>Identificação de comunidades remotas; planificação mensal; mobilização comunitária; realização das brigadas; registo e reporte de dados</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Baixa cobertura em áreas remotas; interrupção das brigadas</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Questoes financeiras afectam a execução na integra do plano das Brigadas nóveis e condições climatéricas</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>988.725</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="3" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr"/>
-      <c r="P69" s="3" t="inlineStr">
+      <c r="R69" s="3" t="inlineStr"/>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr"/>
+      <c r="V69" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_68.html</t>
         </is>
@@ -5511,18 +7563,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Todas as Provincias</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Supervisores capacitados; guias de supervisão; tablets/computadores; transporte; orçamento de deslocação</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
+          <t>Elaborar plano de supervisão; capacitar supervisores; realizar visitas; fornecer feedback; acompanhar planos de melhoria</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Supervisões irregulares; fraca utilização de dados</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Questoes financeiras afectam a execução na integra do plano para implementação das supervisões</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>442.882</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
-      <c r="P70" s="2" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_69.html</t>
         </is>
@@ -5570,18 +7652,44 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Orçamento para produção; especialistas em comunicação; parceria com rádios/TV; materiais IEC; tradução em línguas locais e Disponibilidade de fundos</t>
+        </is>
+      </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>2.270.553</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr"/>
+          <t>Desenvolver mensagens; produzir spots; validar conteúdos; difundir nas rádios e TV; monitorar alcance</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Baixa adesão comunitária; desinformação sobre vacinas</t>
+        </is>
+      </c>
       <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
-      <c r="P71" s="3" t="inlineStr">
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>95.450</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr"/>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>2.270.553</t>
+        </is>
+      </c>
+      <c r="R71" s="3" t="inlineStr"/>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr"/>
+      <c r="V71" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_70.html</t>
         </is>
@@ -5630,20 +7738,50 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
+          <t>Todas as Provincias</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Disponibilidade de vacinas no mercado global e fundo para a sua aquisição; formação de profissionais; actualização do calendário; equipamentos de cadeia de frio; materiais normativos</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Aprovação normativa; planificação da introdução; formação; distribuição inicial; implementação nas maternidades; monitoria de cobertura</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Baixa cobertura da dose ao nascer; dificuldades operacionais</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disponibildade da vacina no mercado global  e a disponiblidade financeira </t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>209.600</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="inlineStr">
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_71.html</t>
         </is>
@@ -5692,20 +7830,50 @@
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
+          <t>8 Provincias (Niassa, Cabo Delgado, Nampula, Tete, Manica, Sofala, Inhambane e Gaza)</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilidade de vacinas no mercado global e fundo para a sua aquisição; formação de vacinadores; expansão da cadeia de frio; materiais de registo; fundos operacionais</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Selecção das províncias; formação das equipas; mobilização comunitária; distribuição das vacinas; implementação; monitoria</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>Introdução lenta; baixa aceitação inicial</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disponibildade da vacina no mercado global  e a disponiblidade financeira </t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr"/>
-      <c r="K73" s="3" t="inlineStr">
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>1.010.053</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr"/>
+      <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="3" t="inlineStr"/>
-      <c r="O73" s="3" t="inlineStr"/>
-      <c r="P73" s="3" t="inlineStr">
+      <c r="R73" s="3" t="inlineStr"/>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr"/>
+      <c r="V73" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_72.html</t>
         </is>
@@ -5752,18 +7920,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros; equipa técnica nacional; equipamentos informáticos; apoio de parceiros</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
+          <t>Planeamento nacional das actividades; definição de normas e orientações técnicas; coordenação com províncias; monitoria de indicadores</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Limitação de financiamento para implementação de actividades</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Dependência de financiamento externo; atrasos na aprovação de fundos</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>6.085.480</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="2" t="inlineStr">
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_73.html</t>
         </is>
@@ -5810,18 +8008,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Técnicos especializados; materiais de formação; plataformas de comunicação; orçamento operacional</t>
+        </is>
+      </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
+          <t>Desenvolvimento de directrizes; capacitação de técnicos provinciais; disseminação de orientações; monitoria da implementação</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Baixa capacidade técnica em alguns níveis do sistema</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Rotatividade de pessoal; insuficiência de formação contínua</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>1.159.429</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr"/>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="3" t="inlineStr"/>
-      <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="3" t="inlineStr"/>
-      <c r="P75" s="3" t="inlineStr">
+      <c r="R75" s="3" t="inlineStr"/>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr"/>
+      <c r="V75" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_74.html</t>
         </is>
@@ -5870,20 +8098,50 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Acesso ao sistema de reporte e disponibilidade financeira</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Recolha e análise de dados; produção de relatórios; feedback às províncias; revisão de desempenho</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Dados incompletos ou atraso no reporte</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Conectividade limitada; fraca cultura de uso de dados</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>1.229.584</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr">
         <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_75.html</t>
         </is>
@@ -5930,18 +8188,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Todas as Provincias</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Equipas provinciais; transporte; equipamentos de cadeia de frio; vacinas e consumíveis; fundos operacionais</t>
+        </is>
+      </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
+          <t>Distribuição de vacinas; supervisão das unidades sanitárias; implementação das actividades de vacinação; monitoria da cobertura</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>Interrupções na disponibilidade de recursos</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilidade financeira; desafios logísticos</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>423.534</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="3" t="inlineStr"/>
-      <c r="P77" s="3" t="inlineStr">
+      <c r="R77" s="3" t="inlineStr"/>
+      <c r="S77" s="3" t="inlineStr"/>
+      <c r="T77" s="3" t="inlineStr"/>
+      <c r="U77" s="3" t="inlineStr"/>
+      <c r="V77" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_76.html</t>
         </is>
@@ -5988,18 +8276,48 @@
           <t>Reduzir a morbi-mortalidade infantil</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para comunicação; produção de materiais IEC; parceria com rádios e TV; especialistas em comunicação</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
+          <t>Desenvolvimento de mensagens; produção de materiais; difusão nacional; monitoria da campanha</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Baixa adesão da população às mensagens de vacinação</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Desinformação; baixo acesso aos meios de comunicação</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>421.745</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
           <t>2.270.553</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/smi/smi_77.html</t>
         </is>
